--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126612557</v>
+        <v>126612201</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589061</v>
+        <v>588980</v>
       </c>
       <c r="R2" t="n">
-        <v>6928145</v>
+        <v>6928023</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126612201</v>
+        <v>126612557</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588980</v>
+        <v>589061</v>
       </c>
       <c r="R4" t="n">
-        <v>6928023</v>
+        <v>6928145</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1083,35 +1083,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126611830</v>
+        <v>126611902</v>
       </c>
       <c r="B6" t="n">
-        <v>96487</v>
+        <v>57578</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
@@ -1180,7 +1188,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126613094</v>
+        <v>126611830</v>
       </c>
       <c r="B7" t="n">
         <v>96487</v>
@@ -1215,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589196</v>
+        <v>588956</v>
       </c>
       <c r="R7" t="n">
-        <v>6928142</v>
+        <v>6927950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,53 +1285,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126611902</v>
+        <v>126613094</v>
       </c>
       <c r="B8" t="n">
-        <v>57578</v>
+        <v>96487</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588956</v>
+        <v>589196</v>
       </c>
       <c r="R8" t="n">
-        <v>6927950</v>
+        <v>6928142</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126612557</v>
+        <v>126612201</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589061</v>
+        <v>588980</v>
       </c>
       <c r="R2" t="n">
-        <v>6928145</v>
+        <v>6928023</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +775,7 @@
         <v>126612079</v>
       </c>
       <c r="B3" t="n">
-        <v>96487</v>
+        <v>96562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126612201</v>
+        <v>126612557</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588980</v>
+        <v>589061</v>
       </c>
       <c r="R4" t="n">
-        <v>6928023</v>
+        <v>6928145</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1086,7 +1086,7 @@
         <v>126611830</v>
       </c>
       <c r="B6" t="n">
-        <v>96487</v>
+        <v>96562</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126613094</v>
       </c>
       <c r="B7" t="n">
-        <v>96487</v>
+        <v>96562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>126614196</v>
       </c>
       <c r="B8" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,50 +1481,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126613466</v>
+        <v>126612248</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>97314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589242</v>
+        <v>588993</v>
       </c>
       <c r="R10" t="n">
-        <v>6928272</v>
+        <v>6928035</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,11 +1552,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,45 +1685,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126612248</v>
+        <v>126613466</v>
       </c>
       <c r="B12" t="n">
-        <v>97239</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588993</v>
+        <v>589242</v>
       </c>
       <c r="R12" t="n">
-        <v>6928035</v>
+        <v>6928272</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,6 +1761,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126612522</v>
+        <v>126612501</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,24 +2017,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
@@ -2044,7 +2049,7 @@
         <v>589049</v>
       </c>
       <c r="R15" t="n">
-        <v>6928131</v>
+        <v>6928118</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,45 +2113,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126613513</v>
+        <v>126613641</v>
       </c>
       <c r="B16" t="n">
-        <v>105396</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589240</v>
+        <v>589253</v>
       </c>
       <c r="R16" t="n">
-        <v>6928277</v>
+        <v>6928222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,6 +2189,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,50 +2220,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126612501</v>
+        <v>126613513</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>105471</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589049</v>
+        <v>589240</v>
       </c>
       <c r="R17" t="n">
-        <v>6928118</v>
+        <v>6928277</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126613641</v>
+        <v>126612522</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>80114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2318,39 +2328,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589253</v>
+        <v>589049</v>
       </c>
       <c r="R18" t="n">
-        <v>6928222</v>
+        <v>6928131</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,11 +2388,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,7 +2524,7 @@
         <v>126612756</v>
       </c>
       <c r="B20" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>126611375</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>126611997</v>
       </c>
       <c r="B23" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>126612297</v>
       </c>
       <c r="B24" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126612201</v>
+        <v>126612079</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>96568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588980</v>
+        <v>588992</v>
       </c>
       <c r="R2" t="n">
-        <v>6928023</v>
+        <v>6928003</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126612079</v>
+        <v>126612201</v>
       </c>
       <c r="B3" t="n">
-        <v>96562</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588992</v>
+        <v>588980</v>
       </c>
       <c r="R3" t="n">
-        <v>6928003</v>
+        <v>6928023</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
         <v>126611830</v>
       </c>
       <c r="B6" t="n">
-        <v>96562</v>
+        <v>96568</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126613094</v>
       </c>
       <c r="B7" t="n">
-        <v>96562</v>
+        <v>96568</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>126614196</v>
       </c>
       <c r="B8" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>126612248</v>
       </c>
       <c r="B10" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>126613513</v>
       </c>
       <c r="B17" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>126612522</v>
       </c>
       <c r="B18" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>126612756</v>
       </c>
       <c r="B20" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>126611375</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,49 +2826,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126611997</v>
+        <v>126612297</v>
       </c>
       <c r="B23" t="n">
-        <v>98353</v>
+        <v>91325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588957</v>
+        <v>589007</v>
       </c>
       <c r="R23" t="n">
-        <v>6927988</v>
+        <v>6928045</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,45 +2923,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126612297</v>
+        <v>126611997</v>
       </c>
       <c r="B24" t="n">
-        <v>91319</v>
+        <v>98359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589007</v>
+        <v>588957</v>
       </c>
       <c r="R24" t="n">
-        <v>6928045</v>
+        <v>6927988</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -1481,45 +1481,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126612248</v>
+        <v>126612632</v>
       </c>
       <c r="B10" t="n">
-        <v>97320</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588993</v>
+        <v>589097</v>
       </c>
       <c r="R10" t="n">
-        <v>6928035</v>
+        <v>6928100</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,6 +1557,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,7 +1588,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126612632</v>
+        <v>126613466</v>
       </c>
       <c r="B11" t="n">
         <v>57657</v>
@@ -1618,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589097</v>
+        <v>589242</v>
       </c>
       <c r="R11" t="n">
-        <v>6928100</v>
+        <v>6928272</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,50 +1695,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126613466</v>
+        <v>126612248</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>97320</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589242</v>
+        <v>588993</v>
       </c>
       <c r="R12" t="n">
-        <v>6928272</v>
+        <v>6928035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1761,11 +1766,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2006,50 +2006,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126612501</v>
+        <v>126613513</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>105477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589049</v>
+        <v>589240</v>
       </c>
       <c r="R15" t="n">
-        <v>6928118</v>
+        <v>6928277</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,11 +2077,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126613641</v>
+        <v>126612501</v>
       </c>
       <c r="B16" t="n">
         <v>57657</v>
@@ -2144,7 +2134,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2153,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589253</v>
+        <v>589049</v>
       </c>
       <c r="R16" t="n">
-        <v>6928222</v>
+        <v>6928118</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,45 +2210,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126613513</v>
+        <v>126613641</v>
       </c>
       <c r="B17" t="n">
-        <v>105477</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589240</v>
+        <v>589253</v>
       </c>
       <c r="R17" t="n">
-        <v>6928277</v>
+        <v>6928222</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2826,45 +2826,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126612297</v>
+        <v>126611997</v>
       </c>
       <c r="B23" t="n">
-        <v>91325</v>
+        <v>98359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589007</v>
+        <v>588957</v>
       </c>
       <c r="R23" t="n">
-        <v>6928045</v>
+        <v>6927988</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,49 +2927,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126611997</v>
+        <v>126612297</v>
       </c>
       <c r="B24" t="n">
-        <v>98359</v>
+        <v>91325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588957</v>
+        <v>589007</v>
       </c>
       <c r="R24" t="n">
-        <v>6927988</v>
+        <v>6928045</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -1481,50 +1481,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126612632</v>
+        <v>126612248</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>97320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589097</v>
+        <v>588993</v>
       </c>
       <c r="R10" t="n">
-        <v>6928100</v>
+        <v>6928035</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,11 +1552,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1588,7 +1578,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126613466</v>
+        <v>126612632</v>
       </c>
       <c r="B11" t="n">
         <v>57657</v>
@@ -1628,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589242</v>
+        <v>589097</v>
       </c>
       <c r="R11" t="n">
-        <v>6928272</v>
+        <v>6928100</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,45 +1685,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126612248</v>
+        <v>126613466</v>
       </c>
       <c r="B12" t="n">
-        <v>97320</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588993</v>
+        <v>589242</v>
       </c>
       <c r="R12" t="n">
-        <v>6928035</v>
+        <v>6928272</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,6 +1761,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3237,6 +3237,1423 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128385756</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91130</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>588904</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6927932</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128386936</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91358</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>588976</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6928045</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128386326</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>588973</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6928008</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128386396</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>588973</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6928008</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128387885</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>589049</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6928118</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128387896</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80164</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>589035</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6928128</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128386843</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>588976</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6928045</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128390318</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>589269</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6928187</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128388697</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>589084</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6928101</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128386976</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>589007</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6928045</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128386182</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92676</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>588927</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6927974</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128386879</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91654</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>658</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>588983</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6928039</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128386897</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91812</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>588976</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6928045</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128387088</v>
+      </c>
+      <c r="B40" t="n">
+        <v>96601</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>588996</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6928070</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3242,7 +3242,7 @@
         <v>128385756</v>
       </c>
       <c r="B27" t="n">
-        <v>91130</v>
+        <v>91133</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>128386936</v>
       </c>
       <c r="B28" t="n">
-        <v>91358</v>
+        <v>91360</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128386396</v>
+        <v>128387885</v>
       </c>
       <c r="B30" t="n">
-        <v>57833</v>
+        <v>80135</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3551,27 +3551,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588973</v>
+        <v>589049</v>
       </c>
       <c r="R30" t="n">
-        <v>6928008</v>
+        <v>6928118</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128387885</v>
+        <v>128386396</v>
       </c>
       <c r="B31" t="n">
-        <v>80135</v>
+        <v>57833</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3653,27 +3653,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589049</v>
+        <v>588973</v>
       </c>
       <c r="R31" t="n">
-        <v>6928118</v>
+        <v>6928008</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4271,7 +4271,7 @@
         <v>128386182</v>
       </c>
       <c r="B37" t="n">
-        <v>92676</v>
+        <v>92678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>128386879</v>
       </c>
       <c r="B38" t="n">
-        <v>91654</v>
+        <v>91656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>128386897</v>
       </c>
       <c r="B39" t="n">
-        <v>91812</v>
+        <v>91814</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>128387088</v>
       </c>
       <c r="B40" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3242,7 +3242,7 @@
         <v>128385756</v>
       </c>
       <c r="B27" t="n">
-        <v>91133</v>
+        <v>91225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>128386936</v>
       </c>
       <c r="B28" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>128386326</v>
       </c>
       <c r="B29" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>128387885</v>
       </c>
       <c r="B30" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>128386396</v>
       </c>
       <c r="B31" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>128387896</v>
       </c>
       <c r="B32" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>128386843</v>
       </c>
       <c r="B33" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>128390318</v>
       </c>
       <c r="B34" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>128388697</v>
       </c>
       <c r="B35" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>128386976</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128386182</v>
       </c>
       <c r="B37" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>128386879</v>
       </c>
       <c r="B38" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>128386897</v>
       </c>
       <c r="B39" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>128387088</v>
       </c>
       <c r="B40" t="n">
-        <v>96603</v>
+        <v>96696</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3239,32 +3239,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128385756</v>
+        <v>128386936</v>
       </c>
       <c r="B27" t="n">
-        <v>91225</v>
+        <v>91452</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588904</v>
+        <v>588976</v>
       </c>
       <c r="R27" t="n">
-        <v>6927932</v>
+        <v>6928045</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,32 +3336,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128386936</v>
+        <v>128385756</v>
       </c>
       <c r="B28" t="n">
-        <v>91452</v>
+        <v>91225</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588976</v>
+        <v>588904</v>
       </c>
       <c r="R28" t="n">
-        <v>6928045</v>
+        <v>6927932</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128387885</v>
+        <v>128386396</v>
       </c>
       <c r="B30" t="n">
-        <v>80188</v>
+        <v>57845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3551,27 +3551,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589049</v>
+        <v>588973</v>
       </c>
       <c r="R30" t="n">
-        <v>6928118</v>
+        <v>6928008</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128386396</v>
+        <v>128387885</v>
       </c>
       <c r="B31" t="n">
-        <v>57845</v>
+        <v>80188</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3653,27 +3653,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588973</v>
+        <v>589049</v>
       </c>
       <c r="R31" t="n">
-        <v>6928008</v>
+        <v>6928118</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3239,32 +3239,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128386936</v>
+        <v>128385756</v>
       </c>
       <c r="B27" t="n">
-        <v>91452</v>
+        <v>91237</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588976</v>
+        <v>588904</v>
       </c>
       <c r="R27" t="n">
-        <v>6928045</v>
+        <v>6927932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,32 +3336,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128385756</v>
+        <v>128386936</v>
       </c>
       <c r="B28" t="n">
-        <v>91225</v>
+        <v>91464</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588904</v>
+        <v>588976</v>
       </c>
       <c r="R28" t="n">
-        <v>6927932</v>
+        <v>6928045</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3436,7 +3436,7 @@
         <v>128386326</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>128386396</v>
       </c>
       <c r="B30" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>128387885</v>
       </c>
       <c r="B31" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>128387896</v>
       </c>
       <c r="B32" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128386843</v>
+        <v>128390318</v>
       </c>
       <c r="B33" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588976</v>
+        <v>589269</v>
       </c>
       <c r="R33" t="n">
-        <v>6928045</v>
+        <v>6928187</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128390318</v>
+        <v>128386843</v>
       </c>
       <c r="B34" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589269</v>
+        <v>588976</v>
       </c>
       <c r="R34" t="n">
-        <v>6928187</v>
+        <v>6928045</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4058,7 +4058,7 @@
         <v>128388697</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>128386976</v>
       </c>
       <c r="B36" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128386182</v>
       </c>
       <c r="B37" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>128386879</v>
       </c>
       <c r="B38" t="n">
-        <v>91748</v>
+        <v>91760</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>128386897</v>
       </c>
       <c r="B39" t="n">
-        <v>91906</v>
+        <v>91918</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>128387088</v>
       </c>
       <c r="B40" t="n">
-        <v>96696</v>
+        <v>96708</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128386396</v>
+        <v>128387885</v>
       </c>
       <c r="B30" t="n">
-        <v>57849</v>
+        <v>80192</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3551,27 +3551,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588973</v>
+        <v>589049</v>
       </c>
       <c r="R30" t="n">
-        <v>6928008</v>
+        <v>6928118</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128387885</v>
+        <v>128386396</v>
       </c>
       <c r="B31" t="n">
-        <v>80192</v>
+        <v>57849</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3653,27 +3653,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589049</v>
+        <v>588973</v>
       </c>
       <c r="R31" t="n">
-        <v>6928118</v>
+        <v>6928008</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3239,32 +3239,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128385756</v>
+        <v>128386936</v>
       </c>
       <c r="B27" t="n">
-        <v>91237</v>
+        <v>91466</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588904</v>
+        <v>588976</v>
       </c>
       <c r="R27" t="n">
-        <v>6927932</v>
+        <v>6928045</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,32 +3336,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128386936</v>
+        <v>128385756</v>
       </c>
       <c r="B28" t="n">
-        <v>91464</v>
+        <v>91239</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588976</v>
+        <v>588904</v>
       </c>
       <c r="R28" t="n">
-        <v>6928045</v>
+        <v>6927932</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3543,7 +3543,7 @@
         <v>128387885</v>
       </c>
       <c r="B30" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>128387896</v>
       </c>
       <c r="B32" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128390318</v>
+        <v>128386843</v>
       </c>
       <c r="B33" t="n">
         <v>57689</v>
@@ -3872,7 +3872,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589269</v>
+        <v>588976</v>
       </c>
       <c r="R33" t="n">
-        <v>6928187</v>
+        <v>6928045</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128386843</v>
+        <v>128390318</v>
       </c>
       <c r="B34" t="n">
         <v>57689</v>
@@ -3979,7 +3979,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588976</v>
+        <v>589269</v>
       </c>
       <c r="R34" t="n">
-        <v>6928045</v>
+        <v>6928187</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4271,7 +4271,7 @@
         <v>128386182</v>
       </c>
       <c r="B37" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>128386879</v>
       </c>
       <c r="B38" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>128386897</v>
       </c>
       <c r="B39" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>128387088</v>
       </c>
       <c r="B40" t="n">
-        <v>96708</v>
+        <v>96710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128387885</v>
+        <v>128386396</v>
       </c>
       <c r="B30" t="n">
-        <v>80194</v>
+        <v>57849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3551,27 +3551,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589049</v>
+        <v>588973</v>
       </c>
       <c r="R30" t="n">
-        <v>6928118</v>
+        <v>6928008</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128386396</v>
+        <v>128387885</v>
       </c>
       <c r="B31" t="n">
-        <v>57849</v>
+        <v>80194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3653,27 +3653,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588973</v>
+        <v>589049</v>
       </c>
       <c r="R31" t="n">
-        <v>6928008</v>
+        <v>6928118</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3336,45 +3336,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128385756</v>
+        <v>128386326</v>
       </c>
       <c r="B28" t="n">
-        <v>91239</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588904</v>
+        <v>588973</v>
       </c>
       <c r="R28" t="n">
-        <v>6927932</v>
+        <v>6928008</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3407,6 +3412,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3433,50 +3443,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128386326</v>
+        <v>128385756</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>91239</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588973</v>
+        <v>588904</v>
       </c>
       <c r="R29" t="n">
-        <v>6928008</v>
+        <v>6927932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3509,11 +3514,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3242,7 +3242,7 @@
         <v>128386936</v>
       </c>
       <c r="B27" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,50 +3336,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128386326</v>
+        <v>128385756</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>91240</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588973</v>
+        <v>588904</v>
       </c>
       <c r="R28" t="n">
-        <v>6928008</v>
+        <v>6927932</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3412,11 +3407,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3443,45 +3433,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128385756</v>
+        <v>128386326</v>
       </c>
       <c r="B29" t="n">
-        <v>91239</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588904</v>
+        <v>588973</v>
       </c>
       <c r="R29" t="n">
-        <v>6927932</v>
+        <v>6928008</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3514,6 +3509,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128386396</v>
+        <v>128387885</v>
       </c>
       <c r="B30" t="n">
-        <v>57849</v>
+        <v>80194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3551,27 +3551,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588973</v>
+        <v>589049</v>
       </c>
       <c r="R30" t="n">
-        <v>6928008</v>
+        <v>6928118</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128387885</v>
+        <v>128386396</v>
       </c>
       <c r="B31" t="n">
-        <v>80194</v>
+        <v>57849</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3653,27 +3653,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589049</v>
+        <v>588973</v>
       </c>
       <c r="R31" t="n">
-        <v>6928118</v>
+        <v>6928008</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3841,7 +3841,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128386843</v>
+        <v>128390318</v>
       </c>
       <c r="B33" t="n">
         <v>57689</v>
@@ -3872,7 +3872,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588976</v>
+        <v>589269</v>
       </c>
       <c r="R33" t="n">
-        <v>6928045</v>
+        <v>6928187</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128390318</v>
+        <v>128386843</v>
       </c>
       <c r="B34" t="n">
         <v>57689</v>
@@ -3979,7 +3979,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589269</v>
+        <v>588976</v>
       </c>
       <c r="R34" t="n">
-        <v>6928187</v>
+        <v>6928045</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4271,7 +4271,7 @@
         <v>128386182</v>
       </c>
       <c r="B37" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>128386879</v>
       </c>
       <c r="B38" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>128386897</v>
       </c>
       <c r="B39" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>128387088</v>
       </c>
       <c r="B40" t="n">
-        <v>96710</v>
+        <v>96711</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3239,32 +3239,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128386936</v>
+        <v>128385756</v>
       </c>
       <c r="B27" t="n">
-        <v>91467</v>
+        <v>91240</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588976</v>
+        <v>588904</v>
       </c>
       <c r="R27" t="n">
-        <v>6928045</v>
+        <v>6927932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,32 +3336,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128385756</v>
+        <v>128386936</v>
       </c>
       <c r="B28" t="n">
-        <v>91240</v>
+        <v>91467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588904</v>
+        <v>588976</v>
       </c>
       <c r="R28" t="n">
-        <v>6927932</v>
+        <v>6928045</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3242,7 +3242,7 @@
         <v>128385756</v>
       </c>
       <c r="B27" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128386936</v>
+        <v>128386326</v>
       </c>
       <c r="B28" t="n">
-        <v>91467</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3347,34 +3347,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588976</v>
+        <v>588973</v>
       </c>
       <c r="R28" t="n">
-        <v>6928045</v>
+        <v>6928008</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3407,6 +3412,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3433,10 +3443,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128386326</v>
+        <v>128386936</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>91494</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3444,39 +3454,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588973</v>
+        <v>588976</v>
       </c>
       <c r="R29" t="n">
-        <v>6928008</v>
+        <v>6928045</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3509,11 +3514,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3543,7 +3543,7 @@
         <v>128387885</v>
       </c>
       <c r="B30" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>128386396</v>
       </c>
       <c r="B31" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>128387896</v>
       </c>
       <c r="B32" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>128390318</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>128386843</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>128388697</v>
       </c>
       <c r="B35" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>128386976</v>
       </c>
       <c r="B36" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>128386182</v>
       </c>
       <c r="B37" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>128386879</v>
       </c>
       <c r="B38" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>128386897</v>
       </c>
       <c r="B39" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>128387088</v>
       </c>
       <c r="B40" t="n">
-        <v>96711</v>
+        <v>96738</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3841,7 +3841,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128390318</v>
+        <v>128386843</v>
       </c>
       <c r="B33" t="n">
         <v>57716</v>
@@ -3872,7 +3872,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589269</v>
+        <v>588976</v>
       </c>
       <c r="R33" t="n">
-        <v>6928187</v>
+        <v>6928045</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128386843</v>
+        <v>128390318</v>
       </c>
       <c r="B34" t="n">
         <v>57716</v>
@@ -3979,7 +3979,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>588976</v>
+        <v>589269</v>
       </c>
       <c r="R34" t="n">
-        <v>6928045</v>
+        <v>6928187</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>126612557</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126613234</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>126613396</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>126612632</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126613466</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>126613429</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>126612730</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>126612501</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>126613641</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>126612770</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>126611535</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>126648165</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>128386326</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>128386843</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>128390318</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>128386976</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>126612557</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126613234</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>126613396</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>126612632</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126613466</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>126613429</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>126612730</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>126612501</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>126613641</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>126612770</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>126611535</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>126648165</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>128386326</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>128386843</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>128390318</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>128386976</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126612079</v>
+        <v>126612201</v>
       </c>
       <c r="B2" t="n">
-        <v>96568</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588992</v>
+        <v>588980</v>
       </c>
       <c r="R2" t="n">
-        <v>6928003</v>
+        <v>6928023</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126612201</v>
+        <v>126612079</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>96562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588980</v>
+        <v>588992</v>
       </c>
       <c r="R3" t="n">
-        <v>6928023</v>
+        <v>6928003</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
         <v>126611830</v>
       </c>
       <c r="B6" t="n">
-        <v>96568</v>
+        <v>96562</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126613094</v>
       </c>
       <c r="B7" t="n">
-        <v>96568</v>
+        <v>96562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>126614196</v>
       </c>
       <c r="B8" t="n">
-        <v>92615</v>
+        <v>92609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>126612248</v>
       </c>
       <c r="B10" t="n">
-        <v>97320</v>
+        <v>97314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2006,45 +2006,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126613513</v>
+        <v>126612501</v>
       </c>
       <c r="B15" t="n">
-        <v>105477</v>
+        <v>57741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589240</v>
+        <v>589049</v>
       </c>
       <c r="R15" t="n">
-        <v>6928277</v>
+        <v>6928118</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126612501</v>
+        <v>126613641</v>
       </c>
       <c r="B16" t="n">
         <v>57741</v>
@@ -2134,7 +2144,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2143,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589049</v>
+        <v>589253</v>
       </c>
       <c r="R16" t="n">
-        <v>6928118</v>
+        <v>6928222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,50 +2220,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126613641</v>
+        <v>126613513</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>105471</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589253</v>
+        <v>589240</v>
       </c>
       <c r="R17" t="n">
-        <v>6928222</v>
+        <v>6928277</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,7 +2320,7 @@
         <v>126612522</v>
       </c>
       <c r="B18" t="n">
-        <v>80117</v>
+        <v>80114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>126612756</v>
       </c>
       <c r="B20" t="n">
-        <v>98359</v>
+        <v>98353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>126611375</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>126611997</v>
       </c>
       <c r="B23" t="n">
-        <v>98359</v>
+        <v>98353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>126612297</v>
       </c>
       <c r="B24" t="n">
-        <v>91325</v>
+        <v>91319</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4645,6 +4645,2915 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132471864</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80458</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>589164</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6928149</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132471838</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>588968</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6928015</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132471845</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>589053</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6928105</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132471859</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92588</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>898</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>589194</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6928151</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132471847</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80451</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>589055</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6928107</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132471858</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92191</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>658</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>589187</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6928156</v>
+      </c>
+      <c r="S46" t="n">
+        <v>6</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132471849</v>
+      </c>
+      <c r="B47" t="n">
+        <v>83163</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>588991</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6928075</v>
+      </c>
+      <c r="S47" t="n">
+        <v>6</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132471840</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>589025</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6928084</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132471862</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80422</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>589162</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6928150</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132471852</v>
+      </c>
+      <c r="B50" t="n">
+        <v>83163</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>588989</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6928023</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132471839</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>589000</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6928044</v>
+      </c>
+      <c r="S51" t="n">
+        <v>8</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132471848</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80422</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>589060</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6928116</v>
+      </c>
+      <c r="S52" t="n">
+        <v>6</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132471861</v>
+      </c>
+      <c r="B53" t="n">
+        <v>83163</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>589209</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6928161</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132471854</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>589097</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6928084</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132471865</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79349</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>185</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>588911</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6927930</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132471841</v>
+      </c>
+      <c r="B56" t="n">
+        <v>83163</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>589035</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6928084</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132471853</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>589101</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6928090</v>
+      </c>
+      <c r="S57" t="n">
+        <v>6</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132471843</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>589031</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6928096</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132472074</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57127</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>589050</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6928091</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132471837</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>588926</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6927968</v>
+      </c>
+      <c r="S60" t="n">
+        <v>9</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132471945</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92620</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>67</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>589033</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6928079</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132471857</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92352</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>589184</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6928132</v>
+      </c>
+      <c r="S62" t="n">
+        <v>6</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132471846</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57127</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>589057</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6928109</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132471836</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79349</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>185</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>588908</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6927957</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132471851</v>
+      </c>
+      <c r="B65" t="n">
+        <v>83163</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>588994</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6928051</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132471856</v>
+      </c>
+      <c r="B66" t="n">
+        <v>83163</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>589129</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6928104</v>
+      </c>
+      <c r="S66" t="n">
+        <v>6</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132471855</v>
+      </c>
+      <c r="B67" t="n">
+        <v>58109</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>589103</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6928093</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -4647,32 +4647,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132471864</v>
+        <v>132471845</v>
       </c>
       <c r="B41" t="n">
-        <v>80458</v>
+        <v>79317</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,13 +4682,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589164</v>
+        <v>589053</v>
       </c>
       <c r="R41" t="n">
-        <v>6928149</v>
+        <v>6928105</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4712,22 +4712,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4754,32 +4754,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132471838</v>
+        <v>132471864</v>
       </c>
       <c r="B42" t="n">
-        <v>79317</v>
+        <v>80458</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588968</v>
+        <v>589164</v>
       </c>
       <c r="R42" t="n">
-        <v>6928015</v>
+        <v>6928149</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4819,22 +4819,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4861,7 +4861,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132471845</v>
+        <v>132471838</v>
       </c>
       <c r="B43" t="n">
         <v>79317</v>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589053</v>
+        <v>588968</v>
       </c>
       <c r="R43" t="n">
-        <v>6928105</v>
+        <v>6928015</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4968,32 +4968,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132471859</v>
+        <v>132471847</v>
       </c>
       <c r="B44" t="n">
-        <v>92588</v>
+        <v>80451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>898</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589194</v>
+        <v>589055</v>
       </c>
       <c r="R44" t="n">
-        <v>6928151</v>
+        <v>6928107</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5033,22 +5033,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5075,32 +5075,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132471847</v>
+        <v>132471859</v>
       </c>
       <c r="B45" t="n">
-        <v>80451</v>
+        <v>92588</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589055</v>
+        <v>589194</v>
       </c>
       <c r="R45" t="n">
-        <v>6928107</v>
+        <v>6928151</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5140,22 +5140,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132471849</v>
+        <v>132471840</v>
       </c>
       <c r="B47" t="n">
-        <v>83163</v>
+        <v>79317</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5324,13 +5324,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>588991</v>
+        <v>589025</v>
       </c>
       <c r="R47" t="n">
-        <v>6928075</v>
+        <v>6928084</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5396,10 +5396,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132471840</v>
+        <v>132471849</v>
       </c>
       <c r="B48" t="n">
-        <v>79317</v>
+        <v>83163</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589025</v>
+        <v>588991</v>
       </c>
       <c r="R48" t="n">
-        <v>6928084</v>
+        <v>6928075</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5717,10 +5717,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132471839</v>
+        <v>132471848</v>
       </c>
       <c r="B51" t="n">
-        <v>79317</v>
+        <v>80422</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5728,21 +5728,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5752,13 +5752,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589000</v>
+        <v>589060</v>
       </c>
       <c r="R51" t="n">
-        <v>6928044</v>
+        <v>6928116</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5824,10 +5824,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132471848</v>
+        <v>132471839</v>
       </c>
       <c r="B52" t="n">
-        <v>80422</v>
+        <v>79317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5859,13 +5859,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589060</v>
+        <v>589000</v>
       </c>
       <c r="R52" t="n">
-        <v>6928116</v>
+        <v>6928044</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7116,10 +7116,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132471836</v>
+        <v>132471851</v>
       </c>
       <c r="B64" t="n">
-        <v>79349</v>
+        <v>83163</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>588908</v>
+        <v>588994</v>
       </c>
       <c r="R64" t="n">
-        <v>6927957</v>
+        <v>6928051</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7223,10 +7223,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132471851</v>
+        <v>132471836</v>
       </c>
       <c r="B65" t="n">
-        <v>83163</v>
+        <v>79349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7234,21 +7234,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>588994</v>
+        <v>588908</v>
       </c>
       <c r="R65" t="n">
-        <v>6928051</v>
+        <v>6927957</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -4647,32 +4647,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132471845</v>
+        <v>132471864</v>
       </c>
       <c r="B41" t="n">
-        <v>79317</v>
+        <v>80460</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,13 +4682,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589053</v>
+        <v>589164</v>
       </c>
       <c r="R41" t="n">
-        <v>6928105</v>
+        <v>6928149</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4712,22 +4712,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4754,32 +4754,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132471864</v>
+        <v>132471845</v>
       </c>
       <c r="B42" t="n">
-        <v>80458</v>
+        <v>79319</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589164</v>
+        <v>589053</v>
       </c>
       <c r="R42" t="n">
-        <v>6928149</v>
+        <v>6928105</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4819,22 +4819,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4864,7 +4864,7 @@
         <v>132471838</v>
       </c>
       <c r="B43" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>132471847</v>
       </c>
       <c r="B44" t="n">
-        <v>80451</v>
+        <v>80453</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>132471859</v>
       </c>
       <c r="B45" t="n">
-        <v>92588</v>
+        <v>92594</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>132471858</v>
       </c>
       <c r="B46" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>132471840</v>
       </c>
       <c r="B47" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>132471849</v>
       </c>
       <c r="B48" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>132471862</v>
       </c>
       <c r="B49" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>132471852</v>
       </c>
       <c r="B50" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>132471848</v>
       </c>
       <c r="B51" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>132471839</v>
       </c>
       <c r="B52" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>132471861</v>
       </c>
       <c r="B53" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132471854</v>
+        <v>132471865</v>
       </c>
       <c r="B54" t="n">
-        <v>91892</v>
+        <v>79351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6049,21 +6049,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589097</v>
+        <v>588911</v>
       </c>
       <c r="R54" t="n">
-        <v>6928084</v>
+        <v>6927930</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6145,10 +6145,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132471865</v>
+        <v>132471854</v>
       </c>
       <c r="B55" t="n">
-        <v>79349</v>
+        <v>91898</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6156,21 +6156,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>588911</v>
+        <v>589097</v>
       </c>
       <c r="R55" t="n">
-        <v>6927930</v>
+        <v>6928084</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6255,7 +6255,7 @@
         <v>132471841</v>
       </c>
       <c r="B56" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>132471853</v>
       </c>
       <c r="B57" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>132471843</v>
       </c>
       <c r="B58" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>132472074</v>
       </c>
       <c r="B59" t="n">
-        <v>57127</v>
+        <v>57128</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6682,48 +6682,51 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132471837</v>
+        <v>132471945</v>
       </c>
       <c r="B60" t="n">
-        <v>79317</v>
+        <v>92626</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>588926</v>
+        <v>589033</v>
       </c>
       <c r="R60" t="n">
-        <v>6927968</v>
+        <v>6928079</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6747,22 +6750,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6771,6 +6764,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6789,51 +6783,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132471945</v>
+        <v>132471837</v>
       </c>
       <c r="B61" t="n">
-        <v>92620</v>
+        <v>79319</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>589033</v>
+        <v>588926</v>
       </c>
       <c r="R61" t="n">
-        <v>6928079</v>
+        <v>6927968</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6857,12 +6848,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6871,7 +6872,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6893,7 +6893,7 @@
         <v>132471857</v>
       </c>
       <c r="B62" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>132471846</v>
       </c>
       <c r="B63" t="n">
-        <v>57127</v>
+        <v>57128</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132471851</v>
+        <v>132471836</v>
       </c>
       <c r="B64" t="n">
-        <v>83163</v>
+        <v>79351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>588994</v>
+        <v>588908</v>
       </c>
       <c r="R64" t="n">
-        <v>6928051</v>
+        <v>6927957</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7223,10 +7223,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132471836</v>
+        <v>132471851</v>
       </c>
       <c r="B65" t="n">
-        <v>79349</v>
+        <v>83165</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7234,21 +7234,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>588908</v>
+        <v>588994</v>
       </c>
       <c r="R65" t="n">
-        <v>6927957</v>
+        <v>6928051</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7333,7 +7333,7 @@
         <v>132471856</v>
       </c>
       <c r="B66" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>132471855</v>
       </c>
       <c r="B67" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -4968,32 +4968,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132471847</v>
+        <v>132471859</v>
       </c>
       <c r="B44" t="n">
-        <v>80453</v>
+        <v>92594</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589055</v>
+        <v>589194</v>
       </c>
       <c r="R44" t="n">
-        <v>6928107</v>
+        <v>6928151</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5033,22 +5033,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5075,32 +5075,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132471859</v>
+        <v>132471847</v>
       </c>
       <c r="B45" t="n">
-        <v>92594</v>
+        <v>80453</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>898</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589194</v>
+        <v>589055</v>
       </c>
       <c r="R45" t="n">
-        <v>6928151</v>
+        <v>6928107</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5140,22 +5140,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6890,48 +6890,60 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132471857</v>
+        <v>132471846</v>
       </c>
       <c r="B62" t="n">
-        <v>92358</v>
+        <v>57128</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589184</v>
+        <v>589057</v>
       </c>
       <c r="R62" t="n">
-        <v>6928132</v>
+        <v>6928109</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6955,22 +6967,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6997,60 +7009,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132471846</v>
+        <v>132471857</v>
       </c>
       <c r="B63" t="n">
-        <v>57128</v>
+        <v>92358</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589057</v>
+        <v>589184</v>
       </c>
       <c r="R63" t="n">
-        <v>6928109</v>
+        <v>6928132</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7074,22 +7074,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7330,10 +7330,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132471856</v>
+        <v>132471855</v>
       </c>
       <c r="B66" t="n">
-        <v>83165</v>
+        <v>58110</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7341,37 +7341,49 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589129</v>
+        <v>589103</v>
       </c>
       <c r="R66" t="n">
-        <v>6928104</v>
+        <v>6928093</v>
       </c>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7400,7 +7412,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7410,7 +7422,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7437,10 +7449,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132471855</v>
+        <v>132471856</v>
       </c>
       <c r="B67" t="n">
-        <v>58110</v>
+        <v>83165</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7448,49 +7460,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589103</v>
+        <v>589129</v>
       </c>
       <c r="R67" t="n">
-        <v>6928093</v>
+        <v>6928104</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -4650,7 +4650,7 @@
         <v>132471864</v>
       </c>
       <c r="B41" t="n">
-        <v>80460</v>
+        <v>80468</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4754,10 +4754,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132471845</v>
+        <v>132471838</v>
       </c>
       <c r="B42" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589053</v>
+        <v>588968</v>
       </c>
       <c r="R42" t="n">
-        <v>6928105</v>
+        <v>6928015</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4861,10 +4861,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132471838</v>
+        <v>132471845</v>
       </c>
       <c r="B43" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588968</v>
+        <v>589053</v>
       </c>
       <c r="R43" t="n">
-        <v>6928015</v>
+        <v>6928105</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4968,32 +4968,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132471859</v>
+        <v>132471847</v>
       </c>
       <c r="B44" t="n">
-        <v>92594</v>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>898</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589194</v>
+        <v>589055</v>
       </c>
       <c r="R44" t="n">
-        <v>6928151</v>
+        <v>6928107</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5033,22 +5033,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5075,32 +5075,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132471847</v>
+        <v>132471859</v>
       </c>
       <c r="B45" t="n">
-        <v>80453</v>
+        <v>92604</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589055</v>
+        <v>589194</v>
       </c>
       <c r="R45" t="n">
-        <v>6928107</v>
+        <v>6928151</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5140,22 +5140,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5185,7 +5185,7 @@
         <v>132471858</v>
       </c>
       <c r="B46" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132471840</v>
+        <v>132471849</v>
       </c>
       <c r="B47" t="n">
-        <v>79319</v>
+        <v>83173</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5324,13 +5324,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589025</v>
+        <v>588991</v>
       </c>
       <c r="R47" t="n">
-        <v>6928084</v>
+        <v>6928075</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5396,10 +5396,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132471849</v>
+        <v>132471840</v>
       </c>
       <c r="B48" t="n">
-        <v>83165</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>588991</v>
+        <v>589025</v>
       </c>
       <c r="R48" t="n">
-        <v>6928075</v>
+        <v>6928084</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5506,7 +5506,7 @@
         <v>132471862</v>
       </c>
       <c r="B49" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>132471852</v>
       </c>
       <c r="B50" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5717,10 +5717,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132471848</v>
+        <v>132471861</v>
       </c>
       <c r="B51" t="n">
-        <v>80424</v>
+        <v>83173</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5728,21 +5728,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5752,13 +5752,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589060</v>
+        <v>589209</v>
       </c>
       <c r="R51" t="n">
-        <v>6928116</v>
+        <v>6928161</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5782,22 +5782,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5824,10 +5824,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132471839</v>
+        <v>132471848</v>
       </c>
       <c r="B52" t="n">
-        <v>79319</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5859,13 +5859,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589000</v>
+        <v>589060</v>
       </c>
       <c r="R52" t="n">
-        <v>6928044</v>
+        <v>6928116</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5931,10 +5931,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132471861</v>
+        <v>132471839</v>
       </c>
       <c r="B53" t="n">
-        <v>83165</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5966,13 +5966,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589209</v>
+        <v>589000</v>
       </c>
       <c r="R53" t="n">
-        <v>6928161</v>
+        <v>6928044</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5996,22 +5996,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6038,10 +6038,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132471865</v>
+        <v>132471854</v>
       </c>
       <c r="B54" t="n">
-        <v>79351</v>
+        <v>91908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6049,21 +6049,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>588911</v>
+        <v>589097</v>
       </c>
       <c r="R54" t="n">
-        <v>6927930</v>
+        <v>6928084</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6145,10 +6145,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132471854</v>
+        <v>132471865</v>
       </c>
       <c r="B55" t="n">
-        <v>91898</v>
+        <v>79359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6156,21 +6156,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589097</v>
+        <v>588911</v>
       </c>
       <c r="R55" t="n">
-        <v>6928084</v>
+        <v>6927930</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6255,7 +6255,7 @@
         <v>132471841</v>
       </c>
       <c r="B56" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>132471853</v>
       </c>
       <c r="B57" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>132471843</v>
       </c>
       <c r="B58" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>132472074</v>
       </c>
       <c r="B59" t="n">
-        <v>57128</v>
+        <v>57132</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6682,51 +6682,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132471945</v>
+        <v>132471837</v>
       </c>
       <c r="B60" t="n">
-        <v>92626</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589033</v>
+        <v>588926</v>
       </c>
       <c r="R60" t="n">
-        <v>6928079</v>
+        <v>6927968</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6750,12 +6747,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6764,7 +6771,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6783,48 +6789,51 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132471837</v>
+        <v>132471945</v>
       </c>
       <c r="B61" t="n">
-        <v>79319</v>
+        <v>92636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>588926</v>
+        <v>589033</v>
       </c>
       <c r="R61" t="n">
-        <v>6927968</v>
+        <v>6928079</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6848,22 +6857,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6872,6 +6871,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6890,60 +6890,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132471846</v>
+        <v>132471857</v>
       </c>
       <c r="B62" t="n">
-        <v>57128</v>
+        <v>92368</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589057</v>
+        <v>589184</v>
       </c>
       <c r="R62" t="n">
-        <v>6928109</v>
+        <v>6928132</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6967,22 +6955,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7009,48 +6997,60 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132471857</v>
+        <v>132471846</v>
       </c>
       <c r="B63" t="n">
-        <v>92358</v>
+        <v>57132</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589184</v>
+        <v>589057</v>
       </c>
       <c r="R63" t="n">
-        <v>6928132</v>
+        <v>6928109</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7074,22 +7074,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7119,7 +7119,7 @@
         <v>132471836</v>
       </c>
       <c r="B64" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>132471851</v>
       </c>
       <c r="B65" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7330,10 +7330,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132471855</v>
+        <v>132471856</v>
       </c>
       <c r="B66" t="n">
-        <v>58110</v>
+        <v>83173</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7341,49 +7341,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589103</v>
+        <v>589129</v>
       </c>
       <c r="R66" t="n">
-        <v>6928093</v>
+        <v>6928104</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7412,7 +7400,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7422,7 +7410,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7449,10 +7437,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132471856</v>
+        <v>132471855</v>
       </c>
       <c r="B67" t="n">
-        <v>83165</v>
+        <v>58114</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7460,37 +7448,49 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589129</v>
+        <v>589103</v>
       </c>
       <c r="R67" t="n">
-        <v>6928104</v>
+        <v>6928093</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4647,32 +4647,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132471864</v>
+        <v>132471845</v>
       </c>
       <c r="B41" t="n">
-        <v>80468</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,13 +4682,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589164</v>
+        <v>589053</v>
       </c>
       <c r="R41" t="n">
-        <v>6928149</v>
+        <v>6928105</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4712,22 +4712,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4754,32 +4754,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132471838</v>
+        <v>132471864</v>
       </c>
       <c r="B42" t="n">
-        <v>79327</v>
+        <v>80468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588968</v>
+        <v>589164</v>
       </c>
       <c r="R42" t="n">
-        <v>6928015</v>
+        <v>6928149</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4819,22 +4819,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4861,7 +4861,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132471845</v>
+        <v>132471838</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589053</v>
+        <v>588968</v>
       </c>
       <c r="R43" t="n">
-        <v>6928105</v>
+        <v>6928015</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4968,32 +4968,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132471847</v>
+        <v>132471859</v>
       </c>
       <c r="B44" t="n">
-        <v>80461</v>
+        <v>92605</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589055</v>
+        <v>589194</v>
       </c>
       <c r="R44" t="n">
-        <v>6928107</v>
+        <v>6928151</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5033,22 +5033,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5075,32 +5075,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132471859</v>
+        <v>132471847</v>
       </c>
       <c r="B45" t="n">
-        <v>92604</v>
+        <v>80461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>898</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589194</v>
+        <v>589055</v>
       </c>
       <c r="R45" t="n">
-        <v>6928151</v>
+        <v>6928107</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5140,22 +5140,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5185,7 +5185,7 @@
         <v>132471858</v>
       </c>
       <c r="B46" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5717,10 +5717,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132471861</v>
+        <v>132471848</v>
       </c>
       <c r="B51" t="n">
-        <v>83173</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5728,21 +5728,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5752,13 +5752,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589209</v>
+        <v>589060</v>
       </c>
       <c r="R51" t="n">
-        <v>6928161</v>
+        <v>6928116</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5782,22 +5782,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5824,10 +5824,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132471848</v>
+        <v>132471839</v>
       </c>
       <c r="B52" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5859,13 +5859,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589060</v>
+        <v>589000</v>
       </c>
       <c r="R52" t="n">
-        <v>6928116</v>
+        <v>6928044</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5931,10 +5931,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132471839</v>
+        <v>132471861</v>
       </c>
       <c r="B53" t="n">
-        <v>79327</v>
+        <v>83173</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5966,13 +5966,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589000</v>
+        <v>589209</v>
       </c>
       <c r="R53" t="n">
-        <v>6928044</v>
+        <v>6928161</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5996,22 +5996,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6041,7 +6041,7 @@
         <v>132471854</v>
       </c>
       <c r="B54" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>132471945</v>
       </c>
       <c r="B61" t="n">
-        <v>92636</v>
+        <v>92637</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>132471857</v>
       </c>
       <c r="B62" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132471836</v>
+        <v>132471851</v>
       </c>
       <c r="B64" t="n">
-        <v>79359</v>
+        <v>83173</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>588908</v>
+        <v>588994</v>
       </c>
       <c r="R64" t="n">
-        <v>6927957</v>
+        <v>6928051</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7223,10 +7223,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132471851</v>
+        <v>132471836</v>
       </c>
       <c r="B65" t="n">
-        <v>83173</v>
+        <v>79359</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7234,21 +7234,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>588994</v>
+        <v>588908</v>
       </c>
       <c r="R65" t="n">
-        <v>6928051</v>
+        <v>6927957</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7554,6 +7554,338 @@
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132758709</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>589115</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6928103</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132758689</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>589145</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6928113</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132758633</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>589149</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6928126</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Två tretåiga hackspettar trummar till varandra.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4754,32 +4754,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132471864</v>
+        <v>132471838</v>
       </c>
       <c r="B42" t="n">
-        <v>80468</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589164</v>
+        <v>588968</v>
       </c>
       <c r="R42" t="n">
-        <v>6928149</v>
+        <v>6928015</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4819,22 +4819,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4861,32 +4861,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132471838</v>
+        <v>132471864</v>
       </c>
       <c r="B43" t="n">
-        <v>79327</v>
+        <v>80468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588968</v>
+        <v>589164</v>
       </c>
       <c r="R43" t="n">
-        <v>6928015</v>
+        <v>6928149</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4926,22 +4926,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4968,32 +4968,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132471859</v>
+        <v>132471847</v>
       </c>
       <c r="B44" t="n">
-        <v>92605</v>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>898</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589194</v>
+        <v>589055</v>
       </c>
       <c r="R44" t="n">
-        <v>6928151</v>
+        <v>6928107</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5033,22 +5033,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5075,32 +5075,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132471847</v>
+        <v>132471859</v>
       </c>
       <c r="B45" t="n">
-        <v>80461</v>
+        <v>92605</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589055</v>
+        <v>589194</v>
       </c>
       <c r="R45" t="n">
-        <v>6928107</v>
+        <v>6928151</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5140,22 +5140,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132471849</v>
+        <v>132471840</v>
       </c>
       <c r="B47" t="n">
-        <v>83173</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5324,13 +5324,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>588991</v>
+        <v>589025</v>
       </c>
       <c r="R47" t="n">
-        <v>6928075</v>
+        <v>6928084</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5396,10 +5396,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132471840</v>
+        <v>132471849</v>
       </c>
       <c r="B48" t="n">
-        <v>79327</v>
+        <v>83173</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589025</v>
+        <v>588991</v>
       </c>
       <c r="R48" t="n">
-        <v>6928084</v>
+        <v>6928075</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6038,10 +6038,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132471854</v>
+        <v>132471865</v>
       </c>
       <c r="B54" t="n">
-        <v>91909</v>
+        <v>79359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6049,21 +6049,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589097</v>
+        <v>588911</v>
       </c>
       <c r="R54" t="n">
-        <v>6928084</v>
+        <v>6927930</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6145,10 +6145,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132471865</v>
+        <v>132471854</v>
       </c>
       <c r="B55" t="n">
-        <v>79359</v>
+        <v>91909</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6156,21 +6156,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>588911</v>
+        <v>589097</v>
       </c>
       <c r="R55" t="n">
-        <v>6927930</v>
+        <v>6928084</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6682,48 +6682,51 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132471837</v>
+        <v>132471945</v>
       </c>
       <c r="B60" t="n">
-        <v>79327</v>
+        <v>92637</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>588926</v>
+        <v>589033</v>
       </c>
       <c r="R60" t="n">
-        <v>6927968</v>
+        <v>6928079</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6747,22 +6750,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6771,6 +6764,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6789,51 +6783,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132471945</v>
+        <v>132471837</v>
       </c>
       <c r="B61" t="n">
-        <v>92637</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>589033</v>
+        <v>588926</v>
       </c>
       <c r="R61" t="n">
-        <v>6928079</v>
+        <v>6927968</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6857,12 +6848,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6871,7 +6872,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132471851</v>
+        <v>132471836</v>
       </c>
       <c r="B64" t="n">
-        <v>83173</v>
+        <v>79359</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>588994</v>
+        <v>588908</v>
       </c>
       <c r="R64" t="n">
-        <v>6928051</v>
+        <v>6927957</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7223,10 +7223,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132471836</v>
+        <v>132471851</v>
       </c>
       <c r="B65" t="n">
-        <v>79359</v>
+        <v>83173</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7234,21 +7234,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>588908</v>
+        <v>588994</v>
       </c>
       <c r="R65" t="n">
-        <v>6927957</v>
+        <v>6928051</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7886,6 +7886,2283 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132785109</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>589218</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6928197</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>132785096</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79359</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>185</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>588974</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6928032</v>
+      </c>
+      <c r="S72" t="n">
+        <v>6</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>132785102</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>589261</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6928183</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>132785098</v>
+      </c>
+      <c r="B74" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>589103</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6928082</v>
+      </c>
+      <c r="S74" t="n">
+        <v>6</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>132785105</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>589267</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6928248</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132785107</v>
+      </c>
+      <c r="B76" t="n">
+        <v>92208</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>658</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>589264</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6928250</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>132785116</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79359</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>185</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>588918</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6927967</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>132785108</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>589231</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6928252</v>
+      </c>
+      <c r="S78" t="n">
+        <v>6</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>132785117</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79351</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>588910</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6927968</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>132785115</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>589083</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6928098</v>
+      </c>
+      <c r="S80" t="n">
+        <v>7</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>132785099</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>589133</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6928102</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>132785101</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>589255</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6928176</v>
+      </c>
+      <c r="S82" t="n">
+        <v>6</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>132785097</v>
+      </c>
+      <c r="B83" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>589067</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6928056</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>132785111</v>
+      </c>
+      <c r="B84" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>589217</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6928189</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>132785106</v>
+      </c>
+      <c r="B85" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>589265</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6928249</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>132785110</v>
+      </c>
+      <c r="B86" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>589217</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6928191</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>132785112</v>
+      </c>
+      <c r="B87" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>589220</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6928181</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>132785114</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>589134</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6928133</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack. Ser ut att vara årsfärskt. Blänkande genomskinlig kåda syns.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>132785104</v>
+      </c>
+      <c r="B89" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>589285</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6928228</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>132785103</v>
+      </c>
+      <c r="B90" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>589277</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6928192</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>132785113</v>
+      </c>
+      <c r="B91" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>589219</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6928180</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -6890,48 +6890,60 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132471857</v>
+        <v>132471846</v>
       </c>
       <c r="B62" t="n">
-        <v>92369</v>
+        <v>57132</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589184</v>
+        <v>589057</v>
       </c>
       <c r="R62" t="n">
-        <v>6928132</v>
+        <v>6928109</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6955,22 +6967,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6997,60 +7009,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132471846</v>
+        <v>132471857</v>
       </c>
       <c r="B63" t="n">
-        <v>57132</v>
+        <v>92369</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589057</v>
+        <v>589184</v>
       </c>
       <c r="R63" t="n">
-        <v>6928109</v>
+        <v>6928132</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7074,22 +7074,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8530,10 +8530,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132785116</v>
+        <v>132785108</v>
       </c>
       <c r="B77" t="n">
-        <v>79359</v>
+        <v>80432</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8565,13 +8565,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>588918</v>
+        <v>589231</v>
       </c>
       <c r="R77" t="n">
-        <v>6927967</v>
+        <v>6928252</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8595,22 +8595,27 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8637,10 +8642,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132785108</v>
+        <v>132785116</v>
       </c>
       <c r="B78" t="n">
-        <v>80432</v>
+        <v>79359</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8648,21 +8653,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8672,13 +8677,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589231</v>
+        <v>588918</v>
       </c>
       <c r="R78" t="n">
-        <v>6928252</v>
+        <v>6927967</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8702,27 +8707,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9391,32 +9391,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132785106</v>
+        <v>132785110</v>
       </c>
       <c r="B85" t="n">
-        <v>92369</v>
+        <v>80432</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9426,10 +9426,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589265</v>
+        <v>589217</v>
       </c>
       <c r="R85" t="n">
-        <v>6928249</v>
+        <v>6928191</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9498,32 +9498,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132785110</v>
+        <v>132785106</v>
       </c>
       <c r="B86" t="n">
-        <v>80432</v>
+        <v>92369</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9533,10 +9533,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589217</v>
+        <v>589265</v>
       </c>
       <c r="R86" t="n">
-        <v>6928191</v>
+        <v>6928249</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9712,53 +9712,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132785114</v>
+        <v>132785104</v>
       </c>
       <c r="B88" t="n">
-        <v>57953</v>
+        <v>80336</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>589134</v>
+        <v>589285</v>
       </c>
       <c r="R88" t="n">
-        <v>6928133</v>
+        <v>6928228</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9790,7 +9782,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9800,12 +9792,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack. Ser ut att vara årsfärskt. Blänkande genomskinlig kåda syns.</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9832,45 +9819,53 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132785104</v>
+        <v>132785114</v>
       </c>
       <c r="B89" t="n">
-        <v>80336</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589285</v>
+        <v>589134</v>
       </c>
       <c r="R89" t="n">
-        <v>6928228</v>
+        <v>6928133</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9902,7 +9897,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9912,7 +9907,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack. Ser ut att vara årsfärskt. Blänkande genomskinlig kåda syns.</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -4647,32 +4647,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132471845</v>
+        <v>132471864</v>
       </c>
       <c r="B41" t="n">
-        <v>79327</v>
+        <v>80468</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,13 +4682,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589053</v>
+        <v>589164</v>
       </c>
       <c r="R41" t="n">
-        <v>6928105</v>
+        <v>6928149</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4712,22 +4712,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4861,32 +4861,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132471864</v>
+        <v>132471845</v>
       </c>
       <c r="B43" t="n">
-        <v>80468</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589164</v>
+        <v>589053</v>
       </c>
       <c r="R43" t="n">
-        <v>6928149</v>
+        <v>6928105</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4926,22 +4926,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4968,32 +4968,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132471847</v>
+        <v>132471859</v>
       </c>
       <c r="B44" t="n">
-        <v>80461</v>
+        <v>92605</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589055</v>
+        <v>589194</v>
       </c>
       <c r="R44" t="n">
-        <v>6928107</v>
+        <v>6928151</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5033,22 +5033,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5075,32 +5075,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132471859</v>
+        <v>132471847</v>
       </c>
       <c r="B45" t="n">
-        <v>92605</v>
+        <v>80461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>898</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589194</v>
+        <v>589055</v>
       </c>
       <c r="R45" t="n">
-        <v>6928151</v>
+        <v>6928107</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5140,22 +5140,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132471840</v>
+        <v>132471849</v>
       </c>
       <c r="B47" t="n">
-        <v>79327</v>
+        <v>83173</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5324,13 +5324,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589025</v>
+        <v>588991</v>
       </c>
       <c r="R47" t="n">
-        <v>6928084</v>
+        <v>6928075</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5396,10 +5396,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132471849</v>
+        <v>132471840</v>
       </c>
       <c r="B48" t="n">
-        <v>83173</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>588991</v>
+        <v>589025</v>
       </c>
       <c r="R48" t="n">
-        <v>6928075</v>
+        <v>6928084</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5717,10 +5717,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132471848</v>
+        <v>132471861</v>
       </c>
       <c r="B51" t="n">
-        <v>80432</v>
+        <v>83173</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5728,21 +5728,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5752,13 +5752,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589060</v>
+        <v>589209</v>
       </c>
       <c r="R51" t="n">
-        <v>6928116</v>
+        <v>6928161</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5782,22 +5782,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5824,10 +5824,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132471839</v>
+        <v>132471848</v>
       </c>
       <c r="B52" t="n">
-        <v>79327</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5859,13 +5859,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589000</v>
+        <v>589060</v>
       </c>
       <c r="R52" t="n">
-        <v>6928044</v>
+        <v>6928116</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5931,10 +5931,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132471861</v>
+        <v>132471839</v>
       </c>
       <c r="B53" t="n">
-        <v>83173</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5966,13 +5966,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589209</v>
+        <v>589000</v>
       </c>
       <c r="R53" t="n">
-        <v>6928161</v>
+        <v>6928044</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5996,22 +5996,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6038,10 +6038,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132471865</v>
+        <v>132471854</v>
       </c>
       <c r="B54" t="n">
-        <v>79359</v>
+        <v>91909</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6049,21 +6049,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>588911</v>
+        <v>589097</v>
       </c>
       <c r="R54" t="n">
-        <v>6927930</v>
+        <v>6928084</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6145,10 +6145,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132471854</v>
+        <v>132471865</v>
       </c>
       <c r="B55" t="n">
-        <v>91909</v>
+        <v>79359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6156,21 +6156,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589097</v>
+        <v>588911</v>
       </c>
       <c r="R55" t="n">
-        <v>6928084</v>
+        <v>6927930</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6890,60 +6890,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132471846</v>
+        <v>132471857</v>
       </c>
       <c r="B62" t="n">
-        <v>57132</v>
+        <v>92369</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589057</v>
+        <v>589184</v>
       </c>
       <c r="R62" t="n">
-        <v>6928109</v>
+        <v>6928132</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6967,22 +6955,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7009,48 +6997,60 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132471857</v>
+        <v>132471846</v>
       </c>
       <c r="B63" t="n">
-        <v>92369</v>
+        <v>57132</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589184</v>
+        <v>589057</v>
       </c>
       <c r="R63" t="n">
-        <v>6928132</v>
+        <v>6928109</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7074,22 +7074,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7116,10 +7116,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132471836</v>
+        <v>132471851</v>
       </c>
       <c r="B64" t="n">
-        <v>79359</v>
+        <v>83173</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7127,21 +7127,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>588908</v>
+        <v>588994</v>
       </c>
       <c r="R64" t="n">
-        <v>6927957</v>
+        <v>6928051</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7223,10 +7223,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132471851</v>
+        <v>132471836</v>
       </c>
       <c r="B65" t="n">
-        <v>83173</v>
+        <v>79359</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7234,21 +7234,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>588994</v>
+        <v>588908</v>
       </c>
       <c r="R65" t="n">
-        <v>6928051</v>
+        <v>6927957</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9939,10 +9939,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132785103</v>
+        <v>132785113</v>
       </c>
       <c r="B90" t="n">
-        <v>58114</v>
+        <v>80432</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9950,46 +9950,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589277</v>
+        <v>589219</v>
       </c>
       <c r="R90" t="n">
-        <v>6928192</v>
+        <v>6928180</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10021,7 +10009,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10031,7 +10019,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10058,10 +10046,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132785113</v>
+        <v>132785103</v>
       </c>
       <c r="B91" t="n">
-        <v>80432</v>
+        <v>58114</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10069,34 +10057,46 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>589219</v>
+        <v>589277</v>
       </c>
       <c r="R91" t="n">
-        <v>6928180</v>
+        <v>6928192</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132471849</v>
+        <v>132471840</v>
       </c>
       <c r="B47" t="n">
-        <v>83173</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5324,13 +5324,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>588991</v>
+        <v>589025</v>
       </c>
       <c r="R47" t="n">
-        <v>6928075</v>
+        <v>6928084</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5396,10 +5396,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132471840</v>
+        <v>132471849</v>
       </c>
       <c r="B48" t="n">
-        <v>79327</v>
+        <v>83173</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589025</v>
+        <v>588991</v>
       </c>
       <c r="R48" t="n">
-        <v>6928084</v>
+        <v>6928075</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -4647,32 +4647,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132471864</v>
+        <v>132471845</v>
       </c>
       <c r="B41" t="n">
-        <v>80468</v>
+        <v>79328</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,13 +4682,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589164</v>
+        <v>589053</v>
       </c>
       <c r="R41" t="n">
-        <v>6928149</v>
+        <v>6928105</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4712,22 +4712,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4754,32 +4754,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132471838</v>
+        <v>132471864</v>
       </c>
       <c r="B42" t="n">
-        <v>79327</v>
+        <v>80469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>588968</v>
+        <v>589164</v>
       </c>
       <c r="R42" t="n">
-        <v>6928015</v>
+        <v>6928149</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4819,22 +4819,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4861,10 +4861,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132471845</v>
+        <v>132471838</v>
       </c>
       <c r="B43" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589053</v>
+        <v>588968</v>
       </c>
       <c r="R43" t="n">
-        <v>6928105</v>
+        <v>6928015</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4971,7 +4971,7 @@
         <v>132471859</v>
       </c>
       <c r="B44" t="n">
-        <v>92605</v>
+        <v>92606</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>132471847</v>
       </c>
       <c r="B45" t="n">
-        <v>80461</v>
+        <v>80462</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>132471858</v>
       </c>
       <c r="B46" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132471840</v>
+        <v>132471849</v>
       </c>
       <c r="B47" t="n">
-        <v>79327</v>
+        <v>83174</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5324,13 +5324,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589025</v>
+        <v>588991</v>
       </c>
       <c r="R47" t="n">
-        <v>6928084</v>
+        <v>6928075</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5396,10 +5396,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132471849</v>
+        <v>132471840</v>
       </c>
       <c r="B48" t="n">
-        <v>83173</v>
+        <v>79328</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>588991</v>
+        <v>589025</v>
       </c>
       <c r="R48" t="n">
-        <v>6928075</v>
+        <v>6928084</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5506,7 +5506,7 @@
         <v>132471862</v>
       </c>
       <c r="B49" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>132471852</v>
       </c>
       <c r="B50" t="n">
-        <v>83173</v>
+        <v>83174</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>132471861</v>
       </c>
       <c r="B51" t="n">
-        <v>83173</v>
+        <v>83174</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>132471848</v>
       </c>
       <c r="B52" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>132471839</v>
       </c>
       <c r="B53" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>132471854</v>
       </c>
       <c r="B54" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>132471865</v>
       </c>
       <c r="B55" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>132471841</v>
       </c>
       <c r="B56" t="n">
-        <v>83173</v>
+        <v>83174</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>132471853</v>
       </c>
       <c r="B57" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>132471843</v>
       </c>
       <c r="B58" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>132472074</v>
       </c>
       <c r="B59" t="n">
-        <v>57132</v>
+        <v>57133</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>132471945</v>
       </c>
       <c r="B60" t="n">
-        <v>92637</v>
+        <v>92638</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>132471837</v>
       </c>
       <c r="B61" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>132471857</v>
       </c>
       <c r="B62" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>132471846</v>
       </c>
       <c r="B63" t="n">
-        <v>57132</v>
+        <v>57133</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>132471851</v>
       </c>
       <c r="B64" t="n">
-        <v>83173</v>
+        <v>83174</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>132471836</v>
       </c>
       <c r="B65" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7330,10 +7330,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132471856</v>
+        <v>132471855</v>
       </c>
       <c r="B66" t="n">
-        <v>83173</v>
+        <v>58115</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7341,37 +7341,49 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589129</v>
+        <v>589103</v>
       </c>
       <c r="R66" t="n">
-        <v>6928104</v>
+        <v>6928093</v>
       </c>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7400,7 +7412,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7410,7 +7422,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7437,10 +7449,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132471855</v>
+        <v>132471856</v>
       </c>
       <c r="B67" t="n">
-        <v>58114</v>
+        <v>83174</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7448,49 +7460,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589103</v>
+        <v>589129</v>
       </c>
       <c r="R67" t="n">
-        <v>6928093</v>
+        <v>6928104</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7559,7 +7559,7 @@
         <v>132758709</v>
       </c>
       <c r="B68" t="n">
-        <v>57132</v>
+        <v>57133</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>132758689</v>
       </c>
       <c r="B69" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>132758633</v>
       </c>
       <c r="B70" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>132785109</v>
       </c>
       <c r="B71" t="n">
-        <v>80461</v>
+        <v>80462</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>132785096</v>
       </c>
       <c r="B72" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>132785102</v>
       </c>
       <c r="B73" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>132785098</v>
       </c>
       <c r="B74" t="n">
-        <v>83173</v>
+        <v>83174</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>132785105</v>
       </c>
       <c r="B75" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>132785107</v>
       </c>
       <c r="B76" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8530,10 +8530,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132785108</v>
+        <v>132785116</v>
       </c>
       <c r="B77" t="n">
-        <v>80432</v>
+        <v>79360</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8565,13 +8565,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>589231</v>
+        <v>588918</v>
       </c>
       <c r="R77" t="n">
-        <v>6928252</v>
+        <v>6927967</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8595,27 +8595,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8642,10 +8637,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132785116</v>
+        <v>132785108</v>
       </c>
       <c r="B78" t="n">
-        <v>79359</v>
+        <v>80433</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8653,21 +8648,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8677,13 +8672,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>588918</v>
+        <v>589231</v>
       </c>
       <c r="R78" t="n">
-        <v>6927967</v>
+        <v>6928252</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8707,22 +8702,27 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8752,7 +8752,7 @@
         <v>132785117</v>
       </c>
       <c r="B79" t="n">
-        <v>79351</v>
+        <v>79352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>132785115</v>
       </c>
       <c r="B80" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>132785099</v>
       </c>
       <c r="B81" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9070,10 +9070,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132785101</v>
+        <v>132785097</v>
       </c>
       <c r="B82" t="n">
-        <v>79327</v>
+        <v>83174</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9081,21 +9081,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9105,13 +9105,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>589255</v>
+        <v>589067</v>
       </c>
       <c r="R82" t="n">
-        <v>6928176</v>
+        <v>6928056</v>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9177,10 +9177,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132785097</v>
+        <v>132785101</v>
       </c>
       <c r="B83" t="n">
-        <v>83173</v>
+        <v>79328</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9188,21 +9188,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9212,13 +9212,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>589067</v>
+        <v>589255</v>
       </c>
       <c r="R83" t="n">
-        <v>6928056</v>
+        <v>6928176</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9287,7 +9287,7 @@
         <v>132785111</v>
       </c>
       <c r="B84" t="n">
-        <v>80461</v>
+        <v>80462</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9391,32 +9391,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132785110</v>
+        <v>132785106</v>
       </c>
       <c r="B85" t="n">
-        <v>80432</v>
+        <v>92370</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9426,10 +9426,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589217</v>
+        <v>589265</v>
       </c>
       <c r="R85" t="n">
-        <v>6928191</v>
+        <v>6928249</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9498,32 +9498,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132785106</v>
+        <v>132785110</v>
       </c>
       <c r="B86" t="n">
-        <v>92369</v>
+        <v>80433</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9533,10 +9533,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589265</v>
+        <v>589217</v>
       </c>
       <c r="R86" t="n">
-        <v>6928249</v>
+        <v>6928191</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9608,7 +9608,7 @@
         <v>132785112</v>
       </c>
       <c r="B87" t="n">
-        <v>80467</v>
+        <v>80468</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>132785104</v>
       </c>
       <c r="B88" t="n">
-        <v>80336</v>
+        <v>80337</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>132785114</v>
       </c>
       <c r="B89" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>132785113</v>
       </c>
       <c r="B90" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>132785103</v>
       </c>
       <c r="B91" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -8956,10 +8956,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132785101</v>
+        <v>132785097</v>
       </c>
       <c r="B81" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8967,21 +8967,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>589255</v>
+        <v>589067</v>
       </c>
       <c r="R81" t="n">
-        <v>6928176</v>
+        <v>6928056</v>
       </c>
       <c r="S81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9063,10 +9063,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132785097</v>
+        <v>132785101</v>
       </c>
       <c r="B82" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9074,21 +9074,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9098,13 +9098,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>589067</v>
+        <v>589255</v>
       </c>
       <c r="R82" t="n">
-        <v>6928056</v>
+        <v>6928176</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9277,32 +9277,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132785106</v>
+        <v>132785110</v>
       </c>
       <c r="B84" t="n">
-        <v>92378</v>
+        <v>80438</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589265</v>
+        <v>589217</v>
       </c>
       <c r="R84" t="n">
-        <v>6928249</v>
+        <v>6928191</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9384,32 +9384,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132785110</v>
+        <v>132785106</v>
       </c>
       <c r="B85" t="n">
-        <v>80438</v>
+        <v>92378</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589217</v>
+        <v>589265</v>
       </c>
       <c r="R85" t="n">
-        <v>6928191</v>
+        <v>6928249</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9825,10 +9825,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132785103</v>
+        <v>132785113</v>
       </c>
       <c r="B89" t="n">
-        <v>58119</v>
+        <v>80438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9836,46 +9836,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589277</v>
+        <v>589219</v>
       </c>
       <c r="R89" t="n">
-        <v>6928192</v>
+        <v>6928180</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9907,7 +9895,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9917,7 +9905,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9944,10 +9932,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132785113</v>
+        <v>132785103</v>
       </c>
       <c r="B90" t="n">
-        <v>80438</v>
+        <v>58119</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9955,34 +9943,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589219</v>
+        <v>589277</v>
       </c>
       <c r="R90" t="n">
-        <v>6928180</v>
+        <v>6928192</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7881,10 +7881,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132785096</v>
+        <v>132785102</v>
       </c>
       <c r="B71" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7916,13 +7916,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>588974</v>
+        <v>589261</v>
       </c>
       <c r="R71" t="n">
-        <v>6928032</v>
+        <v>6928183</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7988,10 +7988,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132785102</v>
+        <v>132785096</v>
       </c>
       <c r="B72" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8023,13 +8023,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>589261</v>
+        <v>588974</v>
       </c>
       <c r="R72" t="n">
-        <v>6928183</v>
+        <v>6928032</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8742,32 +8742,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132785099</v>
+        <v>132785115</v>
       </c>
       <c r="B79" t="n">
-        <v>91881</v>
+        <v>79090</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8777,13 +8777,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589133</v>
+        <v>589083</v>
       </c>
       <c r="R79" t="n">
-        <v>6928102</v>
+        <v>6928098</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8807,22 +8807,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8849,32 +8849,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132785115</v>
+        <v>132785099</v>
       </c>
       <c r="B80" t="n">
-        <v>79090</v>
+        <v>91881</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8884,13 +8884,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589083</v>
+        <v>589133</v>
       </c>
       <c r="R80" t="n">
-        <v>6928098</v>
+        <v>6928102</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8914,22 +8914,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9277,32 +9277,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132785110</v>
+        <v>132785106</v>
       </c>
       <c r="B84" t="n">
-        <v>80438</v>
+        <v>92378</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589217</v>
+        <v>589265</v>
       </c>
       <c r="R84" t="n">
-        <v>6928191</v>
+        <v>6928249</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9384,32 +9384,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132785106</v>
+        <v>132785110</v>
       </c>
       <c r="B85" t="n">
-        <v>92378</v>
+        <v>80438</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589265</v>
+        <v>589217</v>
       </c>
       <c r="R85" t="n">
-        <v>6928249</v>
+        <v>6928191</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10049,6 +10049,541 @@
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>133549786</v>
+      </c>
+      <c r="B91" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Lakatjärnsböcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>589041</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6928112</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>133549781</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79365</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>185</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lakatjärnsböcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>588938</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6927975</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>133549785</v>
+      </c>
+      <c r="B93" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>308</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lakatjärnsböcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>589058</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6928080</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>133549784</v>
+      </c>
+      <c r="B94" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lakatjärnsböcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>589052</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6928089</v>
+      </c>
+      <c r="S94" t="n">
+        <v>11</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>133549777</v>
+      </c>
+      <c r="B95" t="n">
+        <v>93206</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Lakatjärnsböcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>588965</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6928016</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -7881,10 +7881,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132785102</v>
+        <v>132785096</v>
       </c>
       <c r="B71" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7916,13 +7916,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589261</v>
+        <v>588974</v>
       </c>
       <c r="R71" t="n">
-        <v>6928183</v>
+        <v>6928032</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7988,10 +7988,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132785096</v>
+        <v>132785102</v>
       </c>
       <c r="B72" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8023,13 +8023,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>588974</v>
+        <v>589261</v>
       </c>
       <c r="R72" t="n">
-        <v>6928032</v>
+        <v>6928183</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8742,32 +8742,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132785115</v>
+        <v>132785099</v>
       </c>
       <c r="B79" t="n">
-        <v>79090</v>
+        <v>91881</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8777,13 +8777,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589083</v>
+        <v>589133</v>
       </c>
       <c r="R79" t="n">
-        <v>6928098</v>
+        <v>6928102</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8807,22 +8807,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8849,32 +8849,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132785099</v>
+        <v>132785115</v>
       </c>
       <c r="B80" t="n">
-        <v>91881</v>
+        <v>79090</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8884,13 +8884,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589133</v>
+        <v>589083</v>
       </c>
       <c r="R80" t="n">
-        <v>6928102</v>
+        <v>6928098</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8914,22 +8914,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8956,10 +8956,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132785097</v>
+        <v>132785101</v>
       </c>
       <c r="B81" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8967,21 +8967,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>589067</v>
+        <v>589255</v>
       </c>
       <c r="R81" t="n">
-        <v>6928056</v>
+        <v>6928176</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9063,10 +9063,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132785101</v>
+        <v>132785097</v>
       </c>
       <c r="B82" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9074,21 +9074,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9098,13 +9098,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>589255</v>
+        <v>589067</v>
       </c>
       <c r="R82" t="n">
-        <v>6928176</v>
+        <v>6928056</v>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9277,32 +9277,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132785106</v>
+        <v>132785110</v>
       </c>
       <c r="B84" t="n">
-        <v>92378</v>
+        <v>80438</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589265</v>
+        <v>589217</v>
       </c>
       <c r="R84" t="n">
-        <v>6928249</v>
+        <v>6928191</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9384,32 +9384,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132785110</v>
+        <v>132785106</v>
       </c>
       <c r="B85" t="n">
-        <v>80438</v>
+        <v>92378</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589217</v>
+        <v>589265</v>
       </c>
       <c r="R85" t="n">
-        <v>6928191</v>
+        <v>6928249</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9825,10 +9825,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132785113</v>
+        <v>132785103</v>
       </c>
       <c r="B89" t="n">
-        <v>80438</v>
+        <v>58119</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9836,34 +9836,46 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589219</v>
+        <v>589277</v>
       </c>
       <c r="R89" t="n">
-        <v>6928180</v>
+        <v>6928192</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9895,7 +9907,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9905,7 +9917,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9932,10 +9944,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132785103</v>
+        <v>132785113</v>
       </c>
       <c r="B90" t="n">
-        <v>58119</v>
+        <v>80438</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9943,46 +9955,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589277</v>
+        <v>589219</v>
       </c>
       <c r="R90" t="n">
-        <v>6928192</v>
+        <v>6928180</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -8095,10 +8095,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132785098</v>
+        <v>132785105</v>
       </c>
       <c r="B73" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8106,21 +8106,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8130,13 +8130,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589103</v>
+        <v>589267</v>
       </c>
       <c r="R73" t="n">
-        <v>6928082</v>
+        <v>6928248</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8202,10 +8202,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132785105</v>
+        <v>132785098</v>
       </c>
       <c r="B74" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8213,21 +8213,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8237,13 +8237,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589267</v>
+        <v>589103</v>
       </c>
       <c r="R74" t="n">
-        <v>6928248</v>
+        <v>6928082</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9277,32 +9277,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132785110</v>
+        <v>132785106</v>
       </c>
       <c r="B84" t="n">
-        <v>80438</v>
+        <v>92378</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589217</v>
+        <v>589265</v>
       </c>
       <c r="R84" t="n">
-        <v>6928191</v>
+        <v>6928249</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9384,32 +9384,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132785106</v>
+        <v>132785110</v>
       </c>
       <c r="B85" t="n">
-        <v>92378</v>
+        <v>80438</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589265</v>
+        <v>589217</v>
       </c>
       <c r="R85" t="n">
-        <v>6928249</v>
+        <v>6928191</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9825,10 +9825,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132785103</v>
+        <v>132785113</v>
       </c>
       <c r="B89" t="n">
-        <v>58119</v>
+        <v>80438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9836,46 +9836,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589277</v>
+        <v>589219</v>
       </c>
       <c r="R89" t="n">
-        <v>6928192</v>
+        <v>6928180</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9907,7 +9895,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9917,7 +9905,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9944,10 +9932,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132785113</v>
+        <v>132785103</v>
       </c>
       <c r="B90" t="n">
-        <v>80438</v>
+        <v>58119</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9955,34 +9943,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589219</v>
+        <v>589277</v>
       </c>
       <c r="R90" t="n">
-        <v>6928180</v>
+        <v>6928192</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -8095,10 +8095,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132785105</v>
+        <v>132785098</v>
       </c>
       <c r="B73" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8106,21 +8106,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8130,13 +8130,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589267</v>
+        <v>589103</v>
       </c>
       <c r="R73" t="n">
-        <v>6928248</v>
+        <v>6928082</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8202,10 +8202,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132785098</v>
+        <v>132785105</v>
       </c>
       <c r="B74" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8213,21 +8213,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8237,13 +8237,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589103</v>
+        <v>589267</v>
       </c>
       <c r="R74" t="n">
-        <v>6928082</v>
+        <v>6928248</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8742,32 +8742,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132785099</v>
+        <v>132785115</v>
       </c>
       <c r="B79" t="n">
-        <v>91881</v>
+        <v>79090</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8777,13 +8777,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589133</v>
+        <v>589083</v>
       </c>
       <c r="R79" t="n">
-        <v>6928102</v>
+        <v>6928098</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8807,22 +8807,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8849,32 +8849,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132785115</v>
+        <v>132785099</v>
       </c>
       <c r="B80" t="n">
-        <v>79090</v>
+        <v>91881</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8884,13 +8884,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589083</v>
+        <v>589133</v>
       </c>
       <c r="R80" t="n">
-        <v>6928098</v>
+        <v>6928102</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8914,22 +8914,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -7881,10 +7881,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132785096</v>
+        <v>132785102</v>
       </c>
       <c r="B71" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7916,13 +7916,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>588974</v>
+        <v>589261</v>
       </c>
       <c r="R71" t="n">
-        <v>6928032</v>
+        <v>6928183</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7988,10 +7988,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132785102</v>
+        <v>132785096</v>
       </c>
       <c r="B72" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8023,13 +8023,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>589261</v>
+        <v>588974</v>
       </c>
       <c r="R72" t="n">
-        <v>6928183</v>
+        <v>6928032</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8742,32 +8742,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132785115</v>
+        <v>132785099</v>
       </c>
       <c r="B79" t="n">
-        <v>79090</v>
+        <v>91881</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8777,13 +8777,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589083</v>
+        <v>589133</v>
       </c>
       <c r="R79" t="n">
-        <v>6928098</v>
+        <v>6928102</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8807,22 +8807,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8849,32 +8849,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132785099</v>
+        <v>132785115</v>
       </c>
       <c r="B80" t="n">
-        <v>91881</v>
+        <v>79090</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8884,13 +8884,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589133</v>
+        <v>589083</v>
       </c>
       <c r="R80" t="n">
-        <v>6928102</v>
+        <v>6928098</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8914,22 +8914,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9825,10 +9825,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132785113</v>
+        <v>132785103</v>
       </c>
       <c r="B89" t="n">
-        <v>80438</v>
+        <v>58119</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9836,34 +9836,46 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589219</v>
+        <v>589277</v>
       </c>
       <c r="R89" t="n">
-        <v>6928180</v>
+        <v>6928192</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9895,7 +9907,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9905,7 +9917,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9932,10 +9944,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132785103</v>
+        <v>132785113</v>
       </c>
       <c r="B90" t="n">
-        <v>58119</v>
+        <v>80438</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9943,46 +9955,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589277</v>
+        <v>589219</v>
       </c>
       <c r="R90" t="n">
-        <v>6928192</v>
+        <v>6928180</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -7881,10 +7881,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132785102</v>
+        <v>132785096</v>
       </c>
       <c r="B71" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7916,13 +7916,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589261</v>
+        <v>588974</v>
       </c>
       <c r="R71" t="n">
-        <v>6928183</v>
+        <v>6928032</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7988,10 +7988,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132785096</v>
+        <v>132785102</v>
       </c>
       <c r="B72" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8023,13 +8023,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>588974</v>
+        <v>589261</v>
       </c>
       <c r="R72" t="n">
-        <v>6928032</v>
+        <v>6928183</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8742,32 +8742,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132785099</v>
+        <v>132785115</v>
       </c>
       <c r="B79" t="n">
-        <v>91881</v>
+        <v>79090</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8777,13 +8777,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589133</v>
+        <v>589083</v>
       </c>
       <c r="R79" t="n">
-        <v>6928102</v>
+        <v>6928098</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8807,22 +8807,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8849,32 +8849,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132785115</v>
+        <v>132785099</v>
       </c>
       <c r="B80" t="n">
-        <v>79090</v>
+        <v>91881</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8884,13 +8884,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589083</v>
+        <v>589133</v>
       </c>
       <c r="R80" t="n">
-        <v>6928098</v>
+        <v>6928102</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8914,22 +8914,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9825,10 +9825,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132785103</v>
+        <v>132785113</v>
       </c>
       <c r="B89" t="n">
-        <v>58119</v>
+        <v>80438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9836,46 +9836,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589277</v>
+        <v>589219</v>
       </c>
       <c r="R89" t="n">
-        <v>6928192</v>
+        <v>6928180</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9907,7 +9895,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9917,7 +9905,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9944,10 +9932,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132785113</v>
+        <v>132785103</v>
       </c>
       <c r="B90" t="n">
-        <v>80438</v>
+        <v>58119</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9955,34 +9943,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589219</v>
+        <v>589277</v>
       </c>
       <c r="R90" t="n">
-        <v>6928180</v>
+        <v>6928192</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -7881,10 +7881,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132785096</v>
+        <v>132785102</v>
       </c>
       <c r="B71" t="n">
-        <v>79365</v>
+        <v>91918</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7916,13 +7916,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>588974</v>
+        <v>589261</v>
       </c>
       <c r="R71" t="n">
-        <v>6928032</v>
+        <v>6928183</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7988,10 +7988,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132785102</v>
+        <v>132785096</v>
       </c>
       <c r="B72" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8023,13 +8023,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>589261</v>
+        <v>588974</v>
       </c>
       <c r="R72" t="n">
-        <v>6928183</v>
+        <v>6928032</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9825,10 +9825,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132785113</v>
+        <v>132785103</v>
       </c>
       <c r="B89" t="n">
-        <v>80438</v>
+        <v>58119</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9836,34 +9836,46 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589219</v>
+        <v>589277</v>
       </c>
       <c r="R89" t="n">
-        <v>6928180</v>
+        <v>6928192</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9895,7 +9907,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9905,7 +9917,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9932,10 +9944,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132785103</v>
+        <v>132785113</v>
       </c>
       <c r="B90" t="n">
-        <v>58119</v>
+        <v>80438</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9943,46 +9955,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589277</v>
+        <v>589219</v>
       </c>
       <c r="R90" t="n">
-        <v>6928192</v>
+        <v>6928180</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10054,7 +10054,7 @@
         <v>133549786</v>
       </c>
       <c r="B91" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>133549781</v>
       </c>
       <c r="B92" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>133549785</v>
       </c>
       <c r="B93" t="n">
-        <v>83307</v>
+        <v>83308</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>133549784</v>
       </c>
       <c r="B94" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>133549777</v>
       </c>
       <c r="B95" t="n">
-        <v>93206</v>
+        <v>93208</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10583,6 +10583,1290 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>133862336</v>
+      </c>
+      <c r="B96" t="n">
+        <v>83308</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>308</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>589143</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6928139</v>
+      </c>
+      <c r="S96" t="n">
+        <v>6</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>133862333</v>
+      </c>
+      <c r="B97" t="n">
+        <v>83182</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>589103</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6928108</v>
+      </c>
+      <c r="S97" t="n">
+        <v>6</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>133862329</v>
+      </c>
+      <c r="B98" t="n">
+        <v>83308</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>308</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>589005</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6928099</v>
+      </c>
+      <c r="S98" t="n">
+        <v>6</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>133862335</v>
+      </c>
+      <c r="B99" t="n">
+        <v>83316</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>589132</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6928128</v>
+      </c>
+      <c r="S99" t="n">
+        <v>6</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>133862337</v>
+      </c>
+      <c r="B100" t="n">
+        <v>83299</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>589181</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6928156</v>
+      </c>
+      <c r="S100" t="n">
+        <v>8</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>133862331</v>
+      </c>
+      <c r="B101" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>589025</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6928117</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>133862330</v>
+      </c>
+      <c r="B102" t="n">
+        <v>83308</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>308</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>589026</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6928118</v>
+      </c>
+      <c r="S102" t="n">
+        <v>6</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>133862334</v>
+      </c>
+      <c r="B103" t="n">
+        <v>83316</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>589124</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6928125</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>133862338</v>
+      </c>
+      <c r="B104" t="n">
+        <v>83316</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>589113</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6928125</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>133862332</v>
+      </c>
+      <c r="B105" t="n">
+        <v>83316</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>589043</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6928128</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>133862328</v>
+      </c>
+      <c r="B106" t="n">
+        <v>83316</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>589014</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6928075</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>133862327</v>
+      </c>
+      <c r="B107" t="n">
+        <v>89302</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>510</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>588983</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6928051</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -10589,7 +10589,7 @@
         <v>133862336</v>
       </c>
       <c r="B96" t="n">
-        <v>83308</v>
+        <v>83310</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>133862329</v>
       </c>
       <c r="B98" t="n">
-        <v>83308</v>
+        <v>83310</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>133862335</v>
       </c>
       <c r="B99" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>133862337</v>
       </c>
       <c r="B100" t="n">
-        <v>83299</v>
+        <v>83301</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11121,32 +11121,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133862331</v>
+        <v>133862330</v>
       </c>
       <c r="B101" t="n">
-        <v>80467</v>
+        <v>83310</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6461</v>
+        <v>308</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11156,13 +11156,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589025</v>
+        <v>589026</v>
       </c>
       <c r="R101" t="n">
-        <v>6928117</v>
+        <v>6928118</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11228,10 +11228,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862330</v>
+        <v>133862334</v>
       </c>
       <c r="B102" t="n">
-        <v>83308</v>
+        <v>83318</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11239,21 +11239,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,13 +11263,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589026</v>
+        <v>589124</v>
       </c>
       <c r="R102" t="n">
-        <v>6928118</v>
+        <v>6928125</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11335,10 +11335,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133862334</v>
+        <v>133862338</v>
       </c>
       <c r="B103" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589124</v>
+        <v>589113</v>
       </c>
       <c r="R103" t="n">
         <v>6928125</v>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11442,32 +11442,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133862338</v>
+        <v>133862331</v>
       </c>
       <c r="B104" t="n">
-        <v>83316</v>
+        <v>80467</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11477,10 +11477,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589113</v>
+        <v>589025</v>
       </c>
       <c r="R104" t="n">
-        <v>6928125</v>
+        <v>6928117</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11552,7 +11552,7 @@
         <v>133862332</v>
       </c>
       <c r="B105" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>133862328</v>
       </c>
       <c r="B106" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>133862327</v>
       </c>
       <c r="B107" t="n">
-        <v>89302</v>
+        <v>89308</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -10054,7 +10054,7 @@
         <v>133549786</v>
       </c>
       <c r="B91" t="n">
-        <v>83316</v>
+        <v>83319</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>133549785</v>
       </c>
       <c r="B93" t="n">
-        <v>83308</v>
+        <v>83311</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>133549784</v>
       </c>
       <c r="B94" t="n">
-        <v>83316</v>
+        <v>83319</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>133549777</v>
       </c>
       <c r="B95" t="n">
-        <v>93208</v>
+        <v>93216</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>133862336</v>
       </c>
       <c r="B96" t="n">
-        <v>83310</v>
+        <v>83311</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>133862333</v>
       </c>
       <c r="B97" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>133862329</v>
       </c>
       <c r="B98" t="n">
-        <v>83310</v>
+        <v>83311</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>133862335</v>
       </c>
       <c r="B99" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11014,32 +11014,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133862337</v>
+        <v>133862330</v>
       </c>
       <c r="B100" t="n">
-        <v>83301</v>
+        <v>83311</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11049,13 +11049,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589181</v>
+        <v>589026</v>
       </c>
       <c r="R100" t="n">
-        <v>6928156</v>
+        <v>6928118</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11121,32 +11121,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133862330</v>
+        <v>133862337</v>
       </c>
       <c r="B101" t="n">
-        <v>83310</v>
+        <v>83302</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11156,13 +11156,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589026</v>
+        <v>589181</v>
       </c>
       <c r="R101" t="n">
-        <v>6928118</v>
+        <v>6928156</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11228,32 +11228,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862334</v>
+        <v>133862331</v>
       </c>
       <c r="B102" t="n">
-        <v>83318</v>
+        <v>80467</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,10 +11263,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589124</v>
+        <v>589025</v>
       </c>
       <c r="R102" t="n">
-        <v>6928125</v>
+        <v>6928117</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11335,10 +11335,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133862338</v>
+        <v>133862334</v>
       </c>
       <c r="B103" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589113</v>
+        <v>589124</v>
       </c>
       <c r="R103" t="n">
         <v>6928125</v>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11442,32 +11442,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133862331</v>
+        <v>133862338</v>
       </c>
       <c r="B104" t="n">
-        <v>80467</v>
+        <v>83319</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11477,10 +11477,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589025</v>
+        <v>589113</v>
       </c>
       <c r="R104" t="n">
-        <v>6928117</v>
+        <v>6928125</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11552,7 +11552,7 @@
         <v>133862332</v>
       </c>
       <c r="B105" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>133862328</v>
       </c>
       <c r="B106" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>133862327</v>
       </c>
       <c r="B107" t="n">
-        <v>89308</v>
+        <v>89310</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -11014,32 +11014,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133862330</v>
+        <v>133862337</v>
       </c>
       <c r="B100" t="n">
-        <v>83311</v>
+        <v>83302</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11049,13 +11049,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589026</v>
+        <v>589181</v>
       </c>
       <c r="R100" t="n">
-        <v>6928118</v>
+        <v>6928156</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11121,10 +11121,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133862337</v>
+        <v>133862331</v>
       </c>
       <c r="B101" t="n">
-        <v>83302</v>
+        <v>80467</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6439</v>
+        <v>6461</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11156,13 +11156,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589181</v>
+        <v>589025</v>
       </c>
       <c r="R101" t="n">
-        <v>6928156</v>
+        <v>6928117</v>
       </c>
       <c r="S101" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11228,32 +11228,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862331</v>
+        <v>133862334</v>
       </c>
       <c r="B102" t="n">
-        <v>80467</v>
+        <v>83319</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,10 +11263,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589025</v>
+        <v>589124</v>
       </c>
       <c r="R102" t="n">
-        <v>6928117</v>
+        <v>6928125</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11335,7 +11335,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133862334</v>
+        <v>133862338</v>
       </c>
       <c r="B103" t="n">
         <v>83319</v>
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589124</v>
+        <v>589113</v>
       </c>
       <c r="R103" t="n">
         <v>6928125</v>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11442,10 +11442,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133862338</v>
+        <v>133862330</v>
       </c>
       <c r="B104" t="n">
-        <v>83319</v>
+        <v>83311</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11453,21 +11453,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11477,13 +11477,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589113</v>
+        <v>589026</v>
       </c>
       <c r="R104" t="n">
-        <v>6928125</v>
+        <v>6928118</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -11014,32 +11014,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133862337</v>
+        <v>133862330</v>
       </c>
       <c r="B100" t="n">
-        <v>83302</v>
+        <v>83311</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11049,13 +11049,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589181</v>
+        <v>589026</v>
       </c>
       <c r="R100" t="n">
-        <v>6928156</v>
+        <v>6928118</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11121,10 +11121,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133862331</v>
+        <v>133862337</v>
       </c>
       <c r="B101" t="n">
-        <v>80467</v>
+        <v>83302</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6461</v>
+        <v>6439</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11156,13 +11156,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589025</v>
+        <v>589181</v>
       </c>
       <c r="R101" t="n">
-        <v>6928117</v>
+        <v>6928156</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11228,32 +11228,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862334</v>
+        <v>133862331</v>
       </c>
       <c r="B102" t="n">
-        <v>83319</v>
+        <v>80467</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,10 +11263,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589124</v>
+        <v>589025</v>
       </c>
       <c r="R102" t="n">
-        <v>6928125</v>
+        <v>6928117</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11335,7 +11335,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133862338</v>
+        <v>133862334</v>
       </c>
       <c r="B103" t="n">
         <v>83319</v>
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589113</v>
+        <v>589124</v>
       </c>
       <c r="R103" t="n">
         <v>6928125</v>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11442,10 +11442,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133862330</v>
+        <v>133862338</v>
       </c>
       <c r="B104" t="n">
-        <v>83311</v>
+        <v>83319</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11453,21 +11453,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11477,13 +11477,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589026</v>
+        <v>589113</v>
       </c>
       <c r="R104" t="n">
-        <v>6928118</v>
+        <v>6928125</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -10054,7 +10054,7 @@
         <v>133549786</v>
       </c>
       <c r="B91" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>133549781</v>
       </c>
       <c r="B92" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>133549785</v>
       </c>
       <c r="B93" t="n">
-        <v>83311</v>
+        <v>83325</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>133549784</v>
       </c>
       <c r="B94" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>133549777</v>
       </c>
       <c r="B95" t="n">
-        <v>93216</v>
+        <v>93244</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>133862336</v>
       </c>
       <c r="B96" t="n">
-        <v>83311</v>
+        <v>83325</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>133862333</v>
       </c>
       <c r="B97" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>133862329</v>
       </c>
       <c r="B98" t="n">
-        <v>83311</v>
+        <v>83325</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>133862335</v>
       </c>
       <c r="B99" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11014,32 +11014,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133862330</v>
+        <v>133862337</v>
       </c>
       <c r="B100" t="n">
-        <v>83311</v>
+        <v>83316</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11049,13 +11049,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589026</v>
+        <v>589181</v>
       </c>
       <c r="R100" t="n">
-        <v>6928118</v>
+        <v>6928156</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11121,10 +11121,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133862337</v>
+        <v>133862331</v>
       </c>
       <c r="B101" t="n">
-        <v>83302</v>
+        <v>80481</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6439</v>
+        <v>6461</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11156,13 +11156,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589181</v>
+        <v>589025</v>
       </c>
       <c r="R101" t="n">
-        <v>6928156</v>
+        <v>6928117</v>
       </c>
       <c r="S101" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11228,32 +11228,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862331</v>
+        <v>133862330</v>
       </c>
       <c r="B102" t="n">
-        <v>80467</v>
+        <v>83325</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6461</v>
+        <v>308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,13 +11263,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589025</v>
+        <v>589026</v>
       </c>
       <c r="R102" t="n">
-        <v>6928117</v>
+        <v>6928118</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>133862334</v>
       </c>
       <c r="B103" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>133862338</v>
       </c>
       <c r="B104" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>133862332</v>
       </c>
       <c r="B105" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>133862328</v>
       </c>
       <c r="B106" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>133862327</v>
       </c>
       <c r="B107" t="n">
-        <v>89310</v>
+        <v>89328</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -11014,32 +11014,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133862337</v>
+        <v>133862330</v>
       </c>
       <c r="B100" t="n">
-        <v>83316</v>
+        <v>83325</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11049,13 +11049,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589181</v>
+        <v>589026</v>
       </c>
       <c r="R100" t="n">
-        <v>6928156</v>
+        <v>6928118</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11228,32 +11228,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862330</v>
+        <v>133862337</v>
       </c>
       <c r="B102" t="n">
-        <v>83325</v>
+        <v>83316</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,13 +11263,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589026</v>
+        <v>589181</v>
       </c>
       <c r="R102" t="n">
-        <v>6928118</v>
+        <v>6928156</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD102" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -10054,7 +10054,7 @@
         <v>133549786</v>
       </c>
       <c r="B91" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>133549781</v>
       </c>
       <c r="B92" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>133549785</v>
       </c>
       <c r="B93" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>133549784</v>
       </c>
       <c r="B94" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>133549777</v>
       </c>
       <c r="B95" t="n">
-        <v>93244</v>
+        <v>93254</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>133862336</v>
       </c>
       <c r="B96" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>133862333</v>
       </c>
       <c r="B97" t="n">
-        <v>83197</v>
+        <v>83207</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>133862329</v>
       </c>
       <c r="B98" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>133862335</v>
       </c>
       <c r="B99" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11014,32 +11014,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133862330</v>
+        <v>133862337</v>
       </c>
       <c r="B100" t="n">
-        <v>83325</v>
+        <v>83326</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11049,13 +11049,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589026</v>
+        <v>589181</v>
       </c>
       <c r="R100" t="n">
-        <v>6928118</v>
+        <v>6928156</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11124,7 +11124,7 @@
         <v>133862331</v>
       </c>
       <c r="B101" t="n">
-        <v>80481</v>
+        <v>80477</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11228,32 +11228,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862337</v>
+        <v>133862330</v>
       </c>
       <c r="B102" t="n">
-        <v>83316</v>
+        <v>83335</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,13 +11263,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589181</v>
+        <v>589026</v>
       </c>
       <c r="R102" t="n">
-        <v>6928156</v>
+        <v>6928118</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11338,7 +11338,7 @@
         <v>133862334</v>
       </c>
       <c r="B103" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>133862338</v>
       </c>
       <c r="B104" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>133862332</v>
       </c>
       <c r="B105" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>133862328</v>
       </c>
       <c r="B106" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>133862327</v>
       </c>
       <c r="B107" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -11121,32 +11121,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133862331</v>
+        <v>133862330</v>
       </c>
       <c r="B101" t="n">
-        <v>80477</v>
+        <v>83335</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6461</v>
+        <v>308</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11156,13 +11156,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589025</v>
+        <v>589026</v>
       </c>
       <c r="R101" t="n">
-        <v>6928117</v>
+        <v>6928118</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11228,10 +11228,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862330</v>
+        <v>133862334</v>
       </c>
       <c r="B102" t="n">
-        <v>83335</v>
+        <v>83343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11239,21 +11239,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,13 +11263,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589026</v>
+        <v>589124</v>
       </c>
       <c r="R102" t="n">
-        <v>6928118</v>
+        <v>6928125</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11335,32 +11335,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133862334</v>
+        <v>133862331</v>
       </c>
       <c r="B103" t="n">
-        <v>83343</v>
+        <v>80477</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11370,10 +11370,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589124</v>
+        <v>589025</v>
       </c>
       <c r="R103" t="n">
-        <v>6928125</v>
+        <v>6928117</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -11014,10 +11014,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133862337</v>
+        <v>133862331</v>
       </c>
       <c r="B100" t="n">
-        <v>83326</v>
+        <v>80477</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11025,21 +11025,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6439</v>
+        <v>6461</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11049,13 +11049,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589181</v>
+        <v>589025</v>
       </c>
       <c r="R100" t="n">
-        <v>6928156</v>
+        <v>6928117</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11121,10 +11121,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133862330</v>
+        <v>133862338</v>
       </c>
       <c r="B101" t="n">
-        <v>83335</v>
+        <v>83343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11156,13 +11156,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589026</v>
+        <v>589113</v>
       </c>
       <c r="R101" t="n">
-        <v>6928118</v>
+        <v>6928125</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11228,32 +11228,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862334</v>
+        <v>133862337</v>
       </c>
       <c r="B102" t="n">
-        <v>83343</v>
+        <v>83326</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,13 +11263,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589124</v>
+        <v>589181</v>
       </c>
       <c r="R102" t="n">
-        <v>6928125</v>
+        <v>6928156</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11335,32 +11335,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133862331</v>
+        <v>133862330</v>
       </c>
       <c r="B103" t="n">
-        <v>80477</v>
+        <v>83335</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6461</v>
+        <v>308</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589025</v>
+        <v>589026</v>
       </c>
       <c r="R103" t="n">
-        <v>6928117</v>
+        <v>6928118</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133862338</v>
+        <v>133862334</v>
       </c>
       <c r="B104" t="n">
         <v>83343</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589113</v>
+        <v>589124</v>
       </c>
       <c r="R104" t="n">
         <v>6928125</v>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -11014,10 +11014,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133862331</v>
+        <v>133862337</v>
       </c>
       <c r="B100" t="n">
-        <v>80477</v>
+        <v>83326</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11025,21 +11025,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6461</v>
+        <v>6439</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11049,13 +11049,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589025</v>
+        <v>589181</v>
       </c>
       <c r="R100" t="n">
-        <v>6928117</v>
+        <v>6928156</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11121,10 +11121,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133862338</v>
+        <v>133862330</v>
       </c>
       <c r="B101" t="n">
-        <v>83343</v>
+        <v>83335</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11156,13 +11156,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589113</v>
+        <v>589026</v>
       </c>
       <c r="R101" t="n">
-        <v>6928125</v>
+        <v>6928118</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11228,32 +11228,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862337</v>
+        <v>133862334</v>
       </c>
       <c r="B102" t="n">
-        <v>83326</v>
+        <v>83343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,13 +11263,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589181</v>
+        <v>589124</v>
       </c>
       <c r="R102" t="n">
-        <v>6928156</v>
+        <v>6928125</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11335,32 +11335,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133862330</v>
+        <v>133862331</v>
       </c>
       <c r="B103" t="n">
-        <v>83335</v>
+        <v>80477</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>308</v>
+        <v>6461</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589026</v>
+        <v>589025</v>
       </c>
       <c r="R103" t="n">
-        <v>6928118</v>
+        <v>6928117</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133862334</v>
+        <v>133862338</v>
       </c>
       <c r="B104" t="n">
         <v>83343</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589124</v>
+        <v>589113</v>
       </c>
       <c r="R104" t="n">
         <v>6928125</v>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -10054,7 +10054,7 @@
         <v>133549786</v>
       </c>
       <c r="B91" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>133549781</v>
       </c>
       <c r="B92" t="n">
-        <v>79390</v>
+        <v>79391</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>133549785</v>
       </c>
       <c r="B93" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>133549784</v>
       </c>
       <c r="B94" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>133549777</v>
       </c>
       <c r="B95" t="n">
-        <v>93254</v>
+        <v>93256</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>133862336</v>
       </c>
       <c r="B96" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>133862333</v>
       </c>
       <c r="B97" t="n">
-        <v>83207</v>
+        <v>83208</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>133862329</v>
       </c>
       <c r="B98" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>133862335</v>
       </c>
       <c r="B99" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>133862337</v>
       </c>
       <c r="B100" t="n">
-        <v>83326</v>
+        <v>83327</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11121,10 +11121,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133862330</v>
+        <v>133862338</v>
       </c>
       <c r="B101" t="n">
-        <v>83335</v>
+        <v>83344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11156,13 +11156,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589026</v>
+        <v>589113</v>
       </c>
       <c r="R101" t="n">
-        <v>6928118</v>
+        <v>6928125</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11228,32 +11228,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862334</v>
+        <v>133862331</v>
       </c>
       <c r="B102" t="n">
-        <v>83343</v>
+        <v>80478</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,10 +11263,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589124</v>
+        <v>589025</v>
       </c>
       <c r="R102" t="n">
-        <v>6928125</v>
+        <v>6928117</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11335,32 +11335,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133862331</v>
+        <v>133862330</v>
       </c>
       <c r="B103" t="n">
-        <v>80477</v>
+        <v>83336</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6461</v>
+        <v>308</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589025</v>
+        <v>589026</v>
       </c>
       <c r="R103" t="n">
-        <v>6928117</v>
+        <v>6928118</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11442,10 +11442,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133862338</v>
+        <v>133862334</v>
       </c>
       <c r="B104" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589113</v>
+        <v>589124</v>
       </c>
       <c r="R104" t="n">
         <v>6928125</v>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11552,7 +11552,7 @@
         <v>133862332</v>
       </c>
       <c r="B105" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>133862328</v>
       </c>
       <c r="B106" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>133862327</v>
       </c>
       <c r="B107" t="n">
-        <v>89338</v>
+        <v>89339</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -11121,32 +11121,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133862338</v>
+        <v>133862331</v>
       </c>
       <c r="B101" t="n">
-        <v>83344</v>
+        <v>80478</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11156,10 +11156,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589113</v>
+        <v>589025</v>
       </c>
       <c r="R101" t="n">
-        <v>6928125</v>
+        <v>6928117</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11228,32 +11228,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862331</v>
+        <v>133862330</v>
       </c>
       <c r="B102" t="n">
-        <v>80478</v>
+        <v>83336</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6461</v>
+        <v>308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,13 +11263,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589025</v>
+        <v>589026</v>
       </c>
       <c r="R102" t="n">
-        <v>6928117</v>
+        <v>6928118</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11335,10 +11335,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133862330</v>
+        <v>133862334</v>
       </c>
       <c r="B103" t="n">
-        <v>83336</v>
+        <v>83344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11346,21 +11346,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589026</v>
+        <v>589124</v>
       </c>
       <c r="R103" t="n">
-        <v>6928118</v>
+        <v>6928125</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11442,7 +11442,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133862334</v>
+        <v>133862338</v>
       </c>
       <c r="B104" t="n">
         <v>83344</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589124</v>
+        <v>589113</v>
       </c>
       <c r="R104" t="n">
         <v>6928125</v>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -11014,32 +11014,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133862337</v>
+        <v>133862338</v>
       </c>
       <c r="B100" t="n">
-        <v>83327</v>
+        <v>83344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11049,13 +11049,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589181</v>
+        <v>589113</v>
       </c>
       <c r="R100" t="n">
-        <v>6928156</v>
+        <v>6928125</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11121,10 +11121,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133862331</v>
+        <v>133862337</v>
       </c>
       <c r="B101" t="n">
-        <v>80478</v>
+        <v>83327</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6461</v>
+        <v>6439</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11156,13 +11156,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589025</v>
+        <v>589181</v>
       </c>
       <c r="R101" t="n">
-        <v>6928117</v>
+        <v>6928156</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11228,32 +11228,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862334</v>
+        <v>133862331</v>
       </c>
       <c r="B102" t="n">
-        <v>83344</v>
+        <v>80478</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,10 +11263,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589124</v>
+        <v>589025</v>
       </c>
       <c r="R102" t="n">
-        <v>6928125</v>
+        <v>6928117</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11335,10 +11335,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133862330</v>
+        <v>133862334</v>
       </c>
       <c r="B103" t="n">
-        <v>83336</v>
+        <v>83344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11346,21 +11346,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589026</v>
+        <v>589124</v>
       </c>
       <c r="R103" t="n">
-        <v>6928118</v>
+        <v>6928125</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11442,10 +11442,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133862338</v>
+        <v>133862330</v>
       </c>
       <c r="B104" t="n">
-        <v>83344</v>
+        <v>83336</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11453,21 +11453,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11477,13 +11477,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589113</v>
+        <v>589026</v>
       </c>
       <c r="R104" t="n">
-        <v>6928125</v>
+        <v>6928118</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -10589,7 +10589,7 @@
         <v>133862336</v>
       </c>
       <c r="B96" t="n">
-        <v>83336</v>
+        <v>83343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>133862333</v>
       </c>
       <c r="B97" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>133862329</v>
       </c>
       <c r="B98" t="n">
-        <v>83336</v>
+        <v>83343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>133862335</v>
       </c>
       <c r="B99" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11014,32 +11014,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133862338</v>
+        <v>133862331</v>
       </c>
       <c r="B100" t="n">
-        <v>83344</v>
+        <v>80485</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11049,10 +11049,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589113</v>
+        <v>589025</v>
       </c>
       <c r="R100" t="n">
-        <v>6928125</v>
+        <v>6928117</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11124,7 +11124,7 @@
         <v>133862337</v>
       </c>
       <c r="B101" t="n">
-        <v>83327</v>
+        <v>83334</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11228,32 +11228,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862331</v>
+        <v>133862330</v>
       </c>
       <c r="B102" t="n">
-        <v>80478</v>
+        <v>83343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6461</v>
+        <v>308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11263,13 +11263,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589025</v>
+        <v>589026</v>
       </c>
       <c r="R102" t="n">
-        <v>6928117</v>
+        <v>6928118</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>133862334</v>
       </c>
       <c r="B103" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11442,10 +11442,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133862330</v>
+        <v>133862338</v>
       </c>
       <c r="B104" t="n">
-        <v>83336</v>
+        <v>83351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11453,21 +11453,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11477,13 +11477,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589026</v>
+        <v>589113</v>
       </c>
       <c r="R104" t="n">
-        <v>6928118</v>
+        <v>6928125</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11552,7 +11552,7 @@
         <v>133862332</v>
       </c>
       <c r="B105" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>133862328</v>
       </c>
       <c r="B106" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>133862327</v>
       </c>
       <c r="B107" t="n">
-        <v>89340</v>
+        <v>89347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126612079</v>
+        <v>132471945</v>
       </c>
       <c r="B2" t="n">
-        <v>96568</v>
+        <v>92201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588992</v>
+        <v>589033</v>
       </c>
       <c r="R2" t="n">
-        <v>6928003</v>
+        <v>6928079</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126612201</v>
+        <v>132471836</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +811,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588980</v>
+        <v>588908</v>
       </c>
       <c r="R3" t="n">
-        <v>6928023</v>
+        <v>6927957</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126612557</v>
+        <v>132471865</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +894,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589061</v>
+        <v>588911</v>
       </c>
       <c r="R4" t="n">
-        <v>6928145</v>
+        <v>6927930</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -939,17 +948,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126613234</v>
+        <v>132785096</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>79405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,42 +1001,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589242</v>
+        <v>588974</v>
       </c>
       <c r="R5" t="n">
-        <v>6928172</v>
+        <v>6928032</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1046,17 +1055,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,32 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126611830</v>
+        <v>132785116</v>
       </c>
       <c r="B6" t="n">
-        <v>96568</v>
+        <v>79405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,13 +1132,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588956</v>
+        <v>588918</v>
       </c>
       <c r="R6" t="n">
-        <v>6927950</v>
+        <v>6927967</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,12 +1162,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,48 +1204,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126613094</v>
+        <v>133549781</v>
       </c>
       <c r="B7" t="n">
-        <v>96568</v>
+        <v>79405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsböcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589196</v>
+        <v>588938</v>
       </c>
       <c r="R7" t="n">
-        <v>6928142</v>
+        <v>6927975</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,12 +1269,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,48 +1311,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126614196</v>
+        <v>133549785</v>
       </c>
       <c r="B8" t="n">
-        <v>92615</v>
+        <v>83350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsböcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588872</v>
+        <v>589058</v>
       </c>
       <c r="R8" t="n">
-        <v>6927920</v>
+        <v>6928080</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1376,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126613396</v>
+        <v>133862329</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>83350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,42 +1429,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589261</v>
+        <v>589005</v>
       </c>
       <c r="R9" t="n">
-        <v>6928272</v>
+        <v>6928099</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1444,17 +1483,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,32 +1525,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126612248</v>
+        <v>133862330</v>
       </c>
       <c r="B10" t="n">
-        <v>97320</v>
+        <v>83350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,13 +1560,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588993</v>
+        <v>589026</v>
       </c>
       <c r="R10" t="n">
-        <v>6928035</v>
+        <v>6928118</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,12 +1590,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126612632</v>
+        <v>133862336</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>83350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,42 +1643,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589097</v>
+        <v>589143</v>
       </c>
       <c r="R11" t="n">
-        <v>6928100</v>
+        <v>6928139</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1648,17 +1697,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126613466</v>
+        <v>133862327</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>89354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,42 +1750,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589242</v>
+        <v>588983</v>
       </c>
       <c r="R12" t="n">
-        <v>6928272</v>
+        <v>6928051</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1755,17 +1804,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1792,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126613429</v>
+        <v>128386879</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,39 +1857,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589240</v>
+        <v>588983</v>
       </c>
       <c r="R13" t="n">
-        <v>6928277</v>
+        <v>6928039</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,17 +1911,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1943,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126612730</v>
+        <v>132471858</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>92245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1910,42 +1954,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589123</v>
+        <v>589187</v>
       </c>
       <c r="R14" t="n">
-        <v>6928089</v>
+        <v>6928156</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1969,17 +2008,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Årsfärska</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,32 +2050,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126613513</v>
+        <v>132785107</v>
       </c>
       <c r="B15" t="n">
-        <v>105477</v>
+        <v>92245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +2085,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589240</v>
+        <v>589264</v>
       </c>
       <c r="R15" t="n">
-        <v>6928277</v>
+        <v>6928250</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2071,12 +2115,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,53 +2157,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126612501</v>
+        <v>132471859</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>92689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589049</v>
+        <v>589194</v>
       </c>
       <c r="R16" t="n">
-        <v>6928118</v>
+        <v>6928151</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2173,17 +2222,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2210,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126613641</v>
+        <v>126612297</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,39 +2275,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589253</v>
+        <v>589007</v>
       </c>
       <c r="R17" t="n">
-        <v>6928222</v>
+        <v>6928045</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,11 +2335,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126612522</v>
+        <v>128386936</v>
       </c>
       <c r="B18" t="n">
-        <v>80117</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2372,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2396,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589049</v>
+        <v>588976</v>
       </c>
       <c r="R18" t="n">
-        <v>6928131</v>
+        <v>6928045</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,12 +2426,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2414,10 +2458,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126612770</v>
+        <v>132471854</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>91974</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,42 +2469,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589131</v>
+        <v>589097</v>
       </c>
       <c r="R19" t="n">
-        <v>6928090</v>
+        <v>6928084</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2484,17 +2523,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,52 +2565,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126612756</v>
+        <v>132785102</v>
       </c>
       <c r="B20" t="n">
-        <v>98359</v>
+        <v>91974</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589123</v>
+        <v>589261</v>
       </c>
       <c r="R20" t="n">
-        <v>6928089</v>
+        <v>6928183</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2590,12 +2630,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2622,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126611375</v>
+        <v>132785105</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>91974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,21 +2683,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,13 +2707,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588891</v>
+        <v>589267</v>
       </c>
       <c r="R21" t="n">
-        <v>6927920</v>
+        <v>6928248</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2687,12 +2737,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2719,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126611535</v>
+        <v>128386897</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>92369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,39 +2790,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588906</v>
+        <v>588976</v>
       </c>
       <c r="R22" t="n">
-        <v>6927920</v>
+        <v>6928045</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,17 +2844,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2826,52 +2876,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126611997</v>
+        <v>132471857</v>
       </c>
       <c r="B23" t="n">
-        <v>98359</v>
+        <v>92406</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588957</v>
+        <v>589184</v>
       </c>
       <c r="R23" t="n">
-        <v>6927988</v>
+        <v>6928132</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2895,12 +2941,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126612297</v>
+        <v>132785106</v>
       </c>
       <c r="B24" t="n">
-        <v>91325</v>
+        <v>92406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2938,21 +2994,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2962,13 +3018,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589007</v>
+        <v>589265</v>
       </c>
       <c r="R24" t="n">
-        <v>6928045</v>
+        <v>6928249</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2992,12 +3048,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3024,10 +3090,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126648165</v>
+        <v>132471841</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>83222</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3035,45 +3101,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589257</v>
+        <v>589035</v>
       </c>
       <c r="R25" t="n">
-        <v>6928233</v>
+        <v>6928084</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3097,17 +3155,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Fjädrar från tretåig hackspett</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3134,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126611902</v>
+        <v>132471849</v>
       </c>
       <c r="B26" t="n">
-        <v>57578</v>
+        <v>83222</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3145,45 +3208,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100001</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588956</v>
+        <v>588991</v>
       </c>
       <c r="R26" t="n">
-        <v>6927950</v>
+        <v>6928075</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3207,12 +3262,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3239,10 +3304,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128386326</v>
+        <v>132471851</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>83222</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,42 +3315,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588973</v>
+        <v>588994</v>
       </c>
       <c r="R27" t="n">
-        <v>6928008</v>
+        <v>6928051</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3309,17 +3369,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3346,10 +3411,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128386936</v>
+        <v>132471852</v>
       </c>
       <c r="B28" t="n">
-        <v>91513</v>
+        <v>83222</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3357,21 +3422,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,13 +3446,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588976</v>
+        <v>588989</v>
       </c>
       <c r="R28" t="n">
-        <v>6928045</v>
+        <v>6928023</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3411,12 +3476,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3443,32 +3518,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128385756</v>
+        <v>132471856</v>
       </c>
       <c r="B29" t="n">
-        <v>91286</v>
+        <v>83222</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,13 +3553,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588904</v>
+        <v>589129</v>
       </c>
       <c r="R29" t="n">
-        <v>6927932</v>
+        <v>6928104</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3508,12 +3583,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3540,10 +3625,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128386396</v>
+        <v>132471861</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>83222</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3551,42 +3636,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588973</v>
+        <v>589209</v>
       </c>
       <c r="R30" t="n">
-        <v>6928008</v>
+        <v>6928161</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3610,12 +3690,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3642,10 +3732,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128387885</v>
+        <v>132785097</v>
       </c>
       <c r="B31" t="n">
-        <v>80134</v>
+        <v>83222</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3653,42 +3743,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589049</v>
+        <v>589067</v>
       </c>
       <c r="R31" t="n">
-        <v>6928118</v>
+        <v>6928056</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3712,12 +3797,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3744,32 +3839,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128387896</v>
+        <v>132785098</v>
       </c>
       <c r="B32" t="n">
-        <v>80163</v>
+        <v>83222</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3779,13 +3874,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589035</v>
+        <v>589103</v>
       </c>
       <c r="R32" t="n">
-        <v>6928128</v>
+        <v>6928082</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3809,12 +3904,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3841,10 +3946,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128386843</v>
+        <v>133862333</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>83222</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,42 +3957,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588976</v>
+        <v>589103</v>
       </c>
       <c r="R33" t="n">
-        <v>6928045</v>
+        <v>6928108</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3911,17 +4011,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3948,50 +4053,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128390318</v>
+        <v>126611830</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>97231</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589269</v>
+        <v>588956</v>
       </c>
       <c r="R34" t="n">
-        <v>6928187</v>
+        <v>6927950</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,17 +4118,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4055,54 +4150,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128388697</v>
+        <v>126612079</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>97231</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589084</v>
+        <v>588992</v>
       </c>
       <c r="R35" t="n">
-        <v>6928101</v>
+        <v>6928003</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4129,12 +4215,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4161,50 +4247,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128386976</v>
+        <v>126613094</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>97231</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589007</v>
+        <v>589196</v>
       </c>
       <c r="R36" t="n">
-        <v>6928045</v>
+        <v>6928142</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4231,17 +4312,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4268,25 +4344,34 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128386182</v>
+        <v>128387088</v>
       </c>
       <c r="B37" t="n">
-        <v>92832</v>
+        <v>97231</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>2869</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4294,10 +4379,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588927</v>
+        <v>588996</v>
       </c>
       <c r="R37" t="n">
-        <v>6927974</v>
+        <v>6928070</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,32 +4441,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128386897</v>
+        <v>128385756</v>
       </c>
       <c r="B38" t="n">
-        <v>91967</v>
+        <v>91680</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>3215</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4391,10 +4476,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>588976</v>
+        <v>588904</v>
       </c>
       <c r="R38" t="n">
-        <v>6928045</v>
+        <v>6927932</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4453,10 +4538,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128386879</v>
+        <v>126614196</v>
       </c>
       <c r="B39" t="n">
-        <v>91809</v>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4464,21 +4549,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4488,10 +4573,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>588983</v>
+        <v>588872</v>
       </c>
       <c r="R39" t="n">
-        <v>6928039</v>
+        <v>6927920</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4518,12 +4603,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4550,48 +4635,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128387088</v>
+        <v>133549777</v>
       </c>
       <c r="B40" t="n">
-        <v>96762</v>
+        <v>93271</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsböcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>588996</v>
+        <v>588965</v>
       </c>
       <c r="R40" t="n">
-        <v>6928070</v>
+        <v>6928016</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4615,12 +4700,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4647,32 +4742,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132471845</v>
+        <v>132785099</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>91937</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4682,13 +4777,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589053</v>
+        <v>589133</v>
       </c>
       <c r="R41" t="n">
-        <v>6928105</v>
+        <v>6928102</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4712,22 +4807,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4754,32 +4849,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132471864</v>
+        <v>126611375</v>
       </c>
       <c r="B42" t="n">
-        <v>80474</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4789,13 +4884,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589164</v>
+        <v>588891</v>
       </c>
       <c r="R42" t="n">
-        <v>6928149</v>
+        <v>6927920</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4819,22 +4914,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4861,14 +4946,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132471838</v>
+        <v>126612201</v>
       </c>
       <c r="B43" t="n">
-        <v>79333</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4896,13 +4981,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>588968</v>
+        <v>588980</v>
       </c>
       <c r="R43" t="n">
-        <v>6928015</v>
+        <v>6928023</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4926,22 +5011,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>18:17</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>18:17</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4968,10 +5043,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132471859</v>
+        <v>132471837</v>
       </c>
       <c r="B44" t="n">
-        <v>92614</v>
+        <v>79373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4979,21 +5054,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5003,13 +5078,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589194</v>
+        <v>588926</v>
       </c>
       <c r="R44" t="n">
-        <v>6928151</v>
+        <v>6927968</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5033,22 +5108,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5075,32 +5150,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132471847</v>
+        <v>132471838</v>
       </c>
       <c r="B45" t="n">
-        <v>80467</v>
+        <v>79373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,13 +5185,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589055</v>
+        <v>588968</v>
       </c>
       <c r="R45" t="n">
-        <v>6928107</v>
+        <v>6928015</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5145,7 +5220,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5155,7 +5230,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5182,32 +5257,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132471858</v>
+        <v>132471839</v>
       </c>
       <c r="B46" t="n">
-        <v>92217</v>
+        <v>79373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5217,13 +5292,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589187</v>
+        <v>589000</v>
       </c>
       <c r="R46" t="n">
-        <v>6928156</v>
+        <v>6928044</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5247,22 +5322,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5289,32 +5364,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132471849</v>
+        <v>132471840</v>
       </c>
       <c r="B47" t="n">
-        <v>83181</v>
+        <v>79373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5324,13 +5399,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>588991</v>
+        <v>589025</v>
       </c>
       <c r="R47" t="n">
-        <v>6928075</v>
+        <v>6928084</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5359,7 +5434,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5369,7 +5444,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5396,14 +5471,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132471840</v>
+        <v>132471843</v>
       </c>
       <c r="B48" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5431,10 +5506,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589025</v>
+        <v>589031</v>
       </c>
       <c r="R48" t="n">
-        <v>6928084</v>
+        <v>6928096</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5466,7 +5541,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5476,7 +5551,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5503,32 +5578,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132471862</v>
+        <v>132471845</v>
       </c>
       <c r="B49" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5538,13 +5613,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589162</v>
+        <v>589053</v>
       </c>
       <c r="R49" t="n">
-        <v>6928150</v>
+        <v>6928105</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5568,22 +5643,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5610,32 +5685,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132471852</v>
+        <v>132471853</v>
       </c>
       <c r="B50" t="n">
-        <v>83181</v>
+        <v>79373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5645,13 +5720,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>588989</v>
+        <v>589101</v>
       </c>
       <c r="R50" t="n">
-        <v>6928023</v>
+        <v>6928090</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5680,7 +5755,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5690,7 +5765,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5717,32 +5792,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132471848</v>
+        <v>132785101</v>
       </c>
       <c r="B51" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5752,10 +5827,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589060</v>
+        <v>589255</v>
       </c>
       <c r="R51" t="n">
-        <v>6928116</v>
+        <v>6928176</v>
       </c>
       <c r="S51" t="n">
         <v>6</v>
@@ -5782,22 +5857,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5824,32 +5899,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132471839</v>
+        <v>132785117</v>
       </c>
       <c r="B52" t="n">
-        <v>79333</v>
+        <v>79397</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5859,13 +5934,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589000</v>
+        <v>588910</v>
       </c>
       <c r="R52" t="n">
-        <v>6928044</v>
+        <v>6927968</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5889,22 +5964,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5931,32 +6006,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132471861</v>
+        <v>133862337</v>
       </c>
       <c r="B53" t="n">
-        <v>83181</v>
+        <v>83341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6439</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5966,13 +6041,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589209</v>
+        <v>589181</v>
       </c>
       <c r="R53" t="n">
-        <v>6928161</v>
+        <v>6928156</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5996,22 +6071,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6038,10 +6113,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132471854</v>
+        <v>133549784</v>
       </c>
       <c r="B54" t="n">
-        <v>91918</v>
+        <v>83358</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6049,37 +6124,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsböcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589097</v>
+        <v>589052</v>
       </c>
       <c r="R54" t="n">
-        <v>6928084</v>
+        <v>6928089</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6103,22 +6178,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6145,10 +6220,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132471865</v>
+        <v>133549786</v>
       </c>
       <c r="B55" t="n">
-        <v>79365</v>
+        <v>83358</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6156,34 +6231,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsböcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>588911</v>
+        <v>589041</v>
       </c>
       <c r="R55" t="n">
-        <v>6927930</v>
+        <v>6928112</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6210,22 +6285,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6252,10 +6327,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132471841</v>
+        <v>133862328</v>
       </c>
       <c r="B56" t="n">
-        <v>83181</v>
+        <v>83358</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6263,21 +6338,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6287,10 +6362,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589035</v>
+        <v>589014</v>
       </c>
       <c r="R56" t="n">
-        <v>6928084</v>
+        <v>6928075</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6317,22 +6392,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6359,10 +6434,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132471853</v>
+        <v>133862332</v>
       </c>
       <c r="B57" t="n">
-        <v>79333</v>
+        <v>83358</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6370,21 +6445,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6394,13 +6469,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589101</v>
+        <v>589043</v>
       </c>
       <c r="R57" t="n">
-        <v>6928090</v>
+        <v>6928128</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6424,22 +6499,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6466,10 +6541,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132471843</v>
+        <v>133862334</v>
       </c>
       <c r="B58" t="n">
-        <v>79333</v>
+        <v>83358</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6477,21 +6552,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6501,10 +6576,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589031</v>
+        <v>589124</v>
       </c>
       <c r="R58" t="n">
-        <v>6928096</v>
+        <v>6928125</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6531,22 +6606,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6573,10 +6648,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132472074</v>
+        <v>133862335</v>
       </c>
       <c r="B59" t="n">
-        <v>57136</v>
+        <v>83358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6584,49 +6659,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589050</v>
+        <v>589132</v>
       </c>
       <c r="R59" t="n">
-        <v>6928091</v>
+        <v>6928128</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6650,12 +6713,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6682,51 +6755,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132471945</v>
+        <v>133862338</v>
       </c>
       <c r="B60" t="n">
-        <v>92646</v>
+        <v>83358</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>67</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589033</v>
+        <v>589113</v>
       </c>
       <c r="R60" t="n">
-        <v>6928079</v>
+        <v>6928125</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6750,12 +6820,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6764,7 +6844,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6783,10 +6862,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132471837</v>
+        <v>132785115</v>
       </c>
       <c r="B61" t="n">
-        <v>79333</v>
+        <v>79130</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6794,21 +6873,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6818,13 +6897,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>588926</v>
+        <v>589083</v>
       </c>
       <c r="R61" t="n">
-        <v>6927968</v>
+        <v>6928098</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6848,22 +6927,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6890,32 +6969,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132471857</v>
+        <v>132785104</v>
       </c>
       <c r="B62" t="n">
-        <v>92378</v>
+        <v>80382</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6925,13 +7004,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589184</v>
+        <v>589285</v>
       </c>
       <c r="R62" t="n">
-        <v>6928132</v>
+        <v>6928228</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6955,22 +7034,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6997,10 +7076,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132471846</v>
+        <v>126612522</v>
       </c>
       <c r="B63" t="n">
-        <v>57136</v>
+        <v>80432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7008,49 +7087,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589057</v>
+        <v>589049</v>
       </c>
       <c r="R63" t="n">
-        <v>6928109</v>
+        <v>6928131</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7074,22 +7141,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>18:50</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>18:50</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7116,10 +7173,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132471851</v>
+        <v>128387885</v>
       </c>
       <c r="B64" t="n">
-        <v>83181</v>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7127,37 +7184,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>588994</v>
+        <v>589049</v>
       </c>
       <c r="R64" t="n">
-        <v>6928051</v>
+        <v>6928118</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7181,22 +7243,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7223,10 +7275,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132471836</v>
+        <v>132471848</v>
       </c>
       <c r="B65" t="n">
-        <v>79365</v>
+        <v>80488</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7234,21 +7286,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7258,13 +7310,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>588908</v>
+        <v>589060</v>
       </c>
       <c r="R65" t="n">
-        <v>6927957</v>
+        <v>6928116</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7293,7 +7345,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7303,7 +7355,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7330,10 +7382,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132471856</v>
+        <v>132471862</v>
       </c>
       <c r="B66" t="n">
-        <v>83181</v>
+        <v>80488</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7341,21 +7393,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7365,13 +7417,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589129</v>
+        <v>589162</v>
       </c>
       <c r="R66" t="n">
-        <v>6928104</v>
+        <v>6928150</v>
       </c>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7400,7 +7452,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7410,7 +7462,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7437,10 +7489,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132471855</v>
+        <v>132785108</v>
       </c>
       <c r="B67" t="n">
-        <v>58119</v>
+        <v>80488</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7448,49 +7500,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589103</v>
+        <v>589231</v>
       </c>
       <c r="R67" t="n">
-        <v>6928093</v>
+        <v>6928252</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7514,22 +7554,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7556,10 +7601,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132758709</v>
+        <v>132785110</v>
       </c>
       <c r="B68" t="n">
-        <v>57136</v>
+        <v>80488</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7567,49 +7612,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>589115</v>
+        <v>589217</v>
       </c>
       <c r="R68" t="n">
-        <v>6928103</v>
+        <v>6928191</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7633,12 +7666,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7665,10 +7708,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132758689</v>
+        <v>132785113</v>
       </c>
       <c r="B69" t="n">
-        <v>58119</v>
+        <v>80488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7676,49 +7719,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>589145</v>
+        <v>589219</v>
       </c>
       <c r="R69" t="n">
-        <v>6928113</v>
+        <v>6928180</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7742,12 +7773,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7774,10 +7815,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132785109</v>
+        <v>133862331</v>
       </c>
       <c r="B70" t="n">
-        <v>80467</v>
+        <v>80492</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7785,21 +7826,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7809,10 +7850,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589218</v>
+        <v>589025</v>
       </c>
       <c r="R70" t="n">
-        <v>6928197</v>
+        <v>6928117</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7839,22 +7880,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7881,32 +7922,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132785102</v>
+        <v>128387896</v>
       </c>
       <c r="B71" t="n">
-        <v>91918</v>
+        <v>80461</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7916,13 +7957,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589261</v>
+        <v>589035</v>
       </c>
       <c r="R71" t="n">
-        <v>6928183</v>
+        <v>6928128</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7946,22 +7987,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:46</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:46</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7988,32 +8019,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132785096</v>
+        <v>132471847</v>
       </c>
       <c r="B72" t="n">
-        <v>79365</v>
+        <v>80493</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8023,13 +8054,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>588974</v>
+        <v>589055</v>
       </c>
       <c r="R72" t="n">
-        <v>6928032</v>
+        <v>6928107</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8053,22 +8084,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8095,32 +8126,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132785098</v>
+        <v>132785109</v>
       </c>
       <c r="B73" t="n">
-        <v>83181</v>
+        <v>80493</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8130,13 +8161,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589103</v>
+        <v>589218</v>
       </c>
       <c r="R73" t="n">
-        <v>6928082</v>
+        <v>6928197</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8165,7 +8196,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8175,7 +8206,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8202,32 +8233,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132785105</v>
+        <v>132785111</v>
       </c>
       <c r="B74" t="n">
-        <v>91918</v>
+        <v>80493</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8237,10 +8268,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589267</v>
+        <v>589217</v>
       </c>
       <c r="R74" t="n">
-        <v>6928248</v>
+        <v>6928189</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8272,7 +8303,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8282,7 +8313,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8309,32 +8340,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132785107</v>
+        <v>132785112</v>
       </c>
       <c r="B75" t="n">
-        <v>92217</v>
+        <v>80499</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8344,10 +8375,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>589264</v>
+        <v>589220</v>
       </c>
       <c r="R75" t="n">
-        <v>6928250</v>
+        <v>6928181</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8379,7 +8410,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8389,7 +8420,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8416,32 +8447,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132785116</v>
+        <v>132471864</v>
       </c>
       <c r="B76" t="n">
-        <v>79365</v>
+        <v>80500</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8451,10 +8482,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>588918</v>
+        <v>589164</v>
       </c>
       <c r="R76" t="n">
-        <v>6927967</v>
+        <v>6928149</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8481,22 +8512,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8523,10 +8554,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132785108</v>
+        <v>126611902</v>
       </c>
       <c r="B77" t="n">
-        <v>80438</v>
+        <v>57874</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8534,37 +8565,45 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100001</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>589231</v>
+        <v>588956</v>
       </c>
       <c r="R77" t="n">
-        <v>6928252</v>
+        <v>6927950</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8588,27 +8627,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8635,48 +8659,53 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132785117</v>
+        <v>126611439</v>
       </c>
       <c r="B78" t="n">
-        <v>79357</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>588910</v>
+        <v>588906</v>
       </c>
       <c r="R78" t="n">
-        <v>6927968</v>
+        <v>6927920</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8700,22 +8729,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8742,10 +8766,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132785115</v>
+        <v>126612501</v>
       </c>
       <c r="B79" t="n">
-        <v>79090</v>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8753,37 +8777,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589083</v>
+        <v>589049</v>
       </c>
       <c r="R79" t="n">
-        <v>6928098</v>
+        <v>6928118</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8807,22 +8836,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8849,48 +8873,53 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132785099</v>
+        <v>126612557</v>
       </c>
       <c r="B80" t="n">
-        <v>91881</v>
+        <v>57953</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589133</v>
+        <v>589061</v>
       </c>
       <c r="R80" t="n">
-        <v>6928102</v>
+        <v>6928145</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8914,22 +8943,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8956,10 +8980,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132785101</v>
+        <v>126612632</v>
       </c>
       <c r="B81" t="n">
-        <v>79333</v>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8967,37 +8991,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>589255</v>
+        <v>589097</v>
       </c>
       <c r="R81" t="n">
-        <v>6928176</v>
+        <v>6928100</v>
       </c>
       <c r="S81" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9021,22 +9050,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9063,10 +9087,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132785097</v>
+        <v>126612730</v>
       </c>
       <c r="B82" t="n">
-        <v>83181</v>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9074,37 +9098,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>589067</v>
+        <v>589123</v>
       </c>
       <c r="R82" t="n">
-        <v>6928056</v>
+        <v>6928089</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9128,22 +9157,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Årsfärska</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9170,48 +9194,53 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132785111</v>
+        <v>126612770</v>
       </c>
       <c r="B83" t="n">
-        <v>80467</v>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>589217</v>
+        <v>589131</v>
       </c>
       <c r="R83" t="n">
-        <v>6928189</v>
+        <v>6928090</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9235,22 +9264,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9277,48 +9301,53 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132785106</v>
+        <v>126613234</v>
       </c>
       <c r="B84" t="n">
-        <v>92378</v>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589265</v>
+        <v>589242</v>
       </c>
       <c r="R84" t="n">
-        <v>6928249</v>
+        <v>6928172</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9342,22 +9371,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9384,10 +9408,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132785110</v>
+        <v>126613396</v>
       </c>
       <c r="B85" t="n">
-        <v>80438</v>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9395,37 +9419,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589217</v>
+        <v>589261</v>
       </c>
       <c r="R85" t="n">
-        <v>6928191</v>
+        <v>6928272</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9449,22 +9478,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9491,48 +9515,53 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132785112</v>
+        <v>126613429</v>
       </c>
       <c r="B86" t="n">
-        <v>80473</v>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589220</v>
+        <v>589240</v>
       </c>
       <c r="R86" t="n">
-        <v>6928181</v>
+        <v>6928277</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9556,22 +9585,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9598,48 +9622,53 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132785104</v>
+        <v>126613466</v>
       </c>
       <c r="B87" t="n">
-        <v>80342</v>
+        <v>57953</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>589285</v>
+        <v>589242</v>
       </c>
       <c r="R87" t="n">
-        <v>6928228</v>
+        <v>6928272</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9663,22 +9692,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9705,10 +9729,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132785114</v>
+        <v>126613641</v>
       </c>
       <c r="B88" t="n">
-        <v>57958</v>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9734,27 +9758,24 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>589134</v>
+        <v>589253</v>
       </c>
       <c r="R88" t="n">
-        <v>6928133</v>
+        <v>6928222</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9778,27 +9799,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ett färskt ringhack. Ser ut att vara årsfärskt. Blänkande genomskinlig kåda syns.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9825,10 +9836,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132785103</v>
+        <v>126648165</v>
       </c>
       <c r="B89" t="n">
-        <v>58119</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9836,49 +9847,45 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589277</v>
+        <v>589257</v>
       </c>
       <c r="R89" t="n">
-        <v>6928192</v>
+        <v>6928233</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9902,22 +9909,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Fjädrar från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9944,10 +9946,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132785113</v>
+        <v>128386326</v>
       </c>
       <c r="B90" t="n">
-        <v>80438</v>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9955,37 +9957,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589219</v>
+        <v>588973</v>
       </c>
       <c r="R90" t="n">
-        <v>6928180</v>
+        <v>6928008</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10009,22 +10016,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10051,10 +10053,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133549786</v>
+        <v>128386843</v>
       </c>
       <c r="B91" t="n">
-        <v>83344</v>
+        <v>57953</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10062,37 +10064,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lakatjärnsböcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>589041</v>
+        <v>588976</v>
       </c>
       <c r="R91" t="n">
-        <v>6928112</v>
+        <v>6928045</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10116,22 +10123,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10158,10 +10160,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133549781</v>
+        <v>128386976</v>
       </c>
       <c r="B92" t="n">
-        <v>79391</v>
+        <v>57953</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10169,37 +10171,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lakatjärnsböcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>588938</v>
+        <v>589007</v>
       </c>
       <c r="R92" t="n">
-        <v>6927975</v>
+        <v>6928045</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10223,22 +10230,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10265,10 +10267,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133549785</v>
+        <v>128387786</v>
       </c>
       <c r="B93" t="n">
-        <v>83336</v>
+        <v>57953</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10276,37 +10278,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lakatjärnsböcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>589058</v>
+        <v>589011</v>
       </c>
       <c r="R93" t="n">
-        <v>6928080</v>
+        <v>6928137</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10330,22 +10337,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>19:18</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>19:18</t>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10372,10 +10374,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133549784</v>
+        <v>128388697</v>
       </c>
       <c r="B94" t="n">
-        <v>83344</v>
+        <v>57953</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10383,37 +10385,46 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lakatjärnsböcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>589052</v>
+        <v>589084</v>
       </c>
       <c r="R94" t="n">
-        <v>6928089</v>
+        <v>6928101</v>
       </c>
       <c r="S94" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10437,22 +10448,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>18:54</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10479,48 +10480,53 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133549777</v>
+        <v>128390318</v>
       </c>
       <c r="B95" t="n">
-        <v>93257</v>
+        <v>57953</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lakatjärnsböcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>588965</v>
+        <v>589269</v>
       </c>
       <c r="R95" t="n">
-        <v>6928016</v>
+        <v>6928187</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10544,22 +10550,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10586,10 +10587,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133862336</v>
+        <v>132758633</v>
       </c>
       <c r="B96" t="n">
-        <v>83343</v>
+        <v>57954</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10597,37 +10598,49 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>589143</v>
+        <v>589149</v>
       </c>
       <c r="R96" t="n">
-        <v>6928139</v>
+        <v>6928126</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10651,22 +10664,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Två tretåiga hackspettar trummar till varandra.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10693,10 +10701,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133862333</v>
+        <v>132785114</v>
       </c>
       <c r="B97" t="n">
-        <v>83215</v>
+        <v>57975</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10704,37 +10712,45 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>589103</v>
+        <v>589134</v>
       </c>
       <c r="R97" t="n">
-        <v>6928108</v>
+        <v>6928133</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10758,22 +10774,27 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack. Ser ut att vara årsfärskt. Blänkande genomskinlig kåda syns.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10800,48 +10821,60 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133862329</v>
+        <v>132471846</v>
       </c>
       <c r="B98" t="n">
-        <v>83343</v>
+        <v>57153</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>308</v>
+        <v>102612</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>589005</v>
+        <v>589057</v>
       </c>
       <c r="R98" t="n">
-        <v>6928099</v>
+        <v>6928109</v>
       </c>
       <c r="S98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10865,22 +10898,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10907,48 +10940,60 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133862335</v>
+        <v>132472074</v>
       </c>
       <c r="B99" t="n">
-        <v>83351</v>
+        <v>57153</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>589132</v>
+        <v>589050</v>
       </c>
       <c r="R99" t="n">
-        <v>6928128</v>
+        <v>6928091</v>
       </c>
       <c r="S99" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10972,22 +11017,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11014,10 +11049,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133862331</v>
+        <v>132758709</v>
       </c>
       <c r="B100" t="n">
-        <v>80485</v>
+        <v>57153</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11025,37 +11060,49 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6461</v>
+        <v>102612</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589025</v>
+        <v>589115</v>
       </c>
       <c r="R100" t="n">
-        <v>6928117</v>
+        <v>6928103</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11079,22 +11126,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11121,48 +11158,53 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133862337</v>
+        <v>128386396</v>
       </c>
       <c r="B101" t="n">
-        <v>83334</v>
+        <v>58114</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589181</v>
+        <v>588973</v>
       </c>
       <c r="R101" t="n">
-        <v>6928156</v>
+        <v>6928008</v>
       </c>
       <c r="S101" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11186,22 +11228,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>15:39</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>15:39</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11228,10 +11260,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133862330</v>
+        <v>132471855</v>
       </c>
       <c r="B102" t="n">
-        <v>83343</v>
+        <v>58136</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11239,37 +11271,49 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>308</v>
+        <v>103021</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589026</v>
+        <v>589103</v>
       </c>
       <c r="R102" t="n">
-        <v>6928118</v>
+        <v>6928093</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11293,22 +11337,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11335,10 +11379,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133862334</v>
+        <v>132758689</v>
       </c>
       <c r="B103" t="n">
-        <v>83351</v>
+        <v>58136</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11346,37 +11390,49 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589124</v>
+        <v>589145</v>
       </c>
       <c r="R103" t="n">
-        <v>6928125</v>
+        <v>6928113</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11400,22 +11456,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11442,10 +11488,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133862338</v>
+        <v>132785103</v>
       </c>
       <c r="B104" t="n">
-        <v>83351</v>
+        <v>58136</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11453,34 +11499,46 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589113</v>
+        <v>589277</v>
       </c>
       <c r="R104" t="n">
-        <v>6928125</v>
+        <v>6928192</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11507,22 +11565,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11549,48 +11607,52 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133862332</v>
+        <v>126611997</v>
       </c>
       <c r="B105" t="n">
-        <v>83351</v>
+        <v>99035</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6440</v>
+        <v>219790</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>589043</v>
+        <v>588957</v>
       </c>
       <c r="R105" t="n">
-        <v>6928128</v>
+        <v>6927988</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11614,22 +11676,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11656,48 +11708,52 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133862328</v>
+        <v>126612756</v>
       </c>
       <c r="B106" t="n">
-        <v>83351</v>
+        <v>99035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>219790</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>589014</v>
+        <v>589123</v>
       </c>
       <c r="R106" t="n">
-        <v>6928075</v>
+        <v>6928089</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11721,22 +11777,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11763,32 +11809,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133862327</v>
+        <v>126613513</v>
       </c>
       <c r="B107" t="n">
-        <v>89347</v>
+        <v>106244</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>510</v>
+        <v>221144</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11798,13 +11844,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>588983</v>
+        <v>589240</v>
       </c>
       <c r="R107" t="n">
-        <v>6928051</v>
+        <v>6928277</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11828,22 +11874,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11867,6 +11903,103 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>126612248</v>
+      </c>
+      <c r="B108" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>588993</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6928035</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -3046,6 +3046,10 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
@@ -3104,8 +3108,9 @@
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY131"/>
+  <dimension ref="A1:AY138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132471836</v>
+        <v>135276297</v>
       </c>
       <c r="B7" t="n">
-        <v>79405</v>
+        <v>91924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588908</v>
+        <v>589121</v>
       </c>
       <c r="R7" t="n">
-        <v>6927957</v>
+        <v>6928130</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132471865</v>
+        <v>132471836</v>
       </c>
       <c r="B8" t="n">
         <v>79405</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588911</v>
+        <v>588908</v>
       </c>
       <c r="R8" t="n">
-        <v>6927930</v>
+        <v>6927957</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1385,22 +1385,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132785096</v>
+        <v>132471865</v>
       </c>
       <c r="B9" t="n">
         <v>79405</v>
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588974</v>
+        <v>588911</v>
       </c>
       <c r="R9" t="n">
-        <v>6928032</v>
+        <v>6927930</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1492,22 +1492,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1534,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132785116</v>
+        <v>132785096</v>
       </c>
       <c r="B10" t="n">
         <v>79405</v>
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588918</v>
+        <v>588974</v>
       </c>
       <c r="R10" t="n">
-        <v>6927967</v>
+        <v>6928032</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1599,22 +1599,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133549781</v>
+        <v>132785116</v>
       </c>
       <c r="B11" t="n">
         <v>79405</v>
@@ -1672,14 +1672,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lakatjärnsböcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588938</v>
+        <v>588918</v>
       </c>
       <c r="R11" t="n">
-        <v>6927975</v>
+        <v>6927967</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1706,22 +1706,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,7 +1748,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134822277</v>
+        <v>133549781</v>
       </c>
       <c r="B12" t="n">
         <v>79405</v>
@@ -1779,14 +1779,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsböcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588925</v>
+        <v>588938</v>
       </c>
       <c r="R12" t="n">
-        <v>6927973</v>
+        <v>6927975</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133549785</v>
+        <v>134822277</v>
       </c>
       <c r="B13" t="n">
-        <v>83350</v>
+        <v>79405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,34 +1866,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lakatjärnsböcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589058</v>
+        <v>588925</v>
       </c>
       <c r="R13" t="n">
-        <v>6928080</v>
+        <v>6927973</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1920,22 +1920,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133862329</v>
+        <v>133549785</v>
       </c>
       <c r="B14" t="n">
         <v>83350</v>
@@ -1993,17 +1993,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsböcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589005</v>
+        <v>589058</v>
       </c>
       <c r="R14" t="n">
-        <v>6928099</v>
+        <v>6928080</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2027,22 +2027,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133862330</v>
+        <v>133862329</v>
       </c>
       <c r="B15" t="n">
         <v>83350</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589026</v>
+        <v>589005</v>
       </c>
       <c r="R15" t="n">
-        <v>6928118</v>
+        <v>6928099</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,7 +2176,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133862336</v>
+        <v>133862330</v>
       </c>
       <c r="B16" t="n">
         <v>83350</v>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589143</v>
+        <v>589026</v>
       </c>
       <c r="R16" t="n">
-        <v>6928139</v>
+        <v>6928118</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,10 +2283,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133862327</v>
+        <v>133862336</v>
       </c>
       <c r="B17" t="n">
-        <v>89354</v>
+        <v>83350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,21 +2294,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2318,13 +2318,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588983</v>
+        <v>589143</v>
       </c>
       <c r="R17" t="n">
-        <v>6928051</v>
+        <v>6928139</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128386879</v>
+        <v>133862327</v>
       </c>
       <c r="B18" t="n">
-        <v>92208</v>
+        <v>89354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2401,21 +2401,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2428,10 +2428,10 @@
         <v>588983</v>
       </c>
       <c r="R18" t="n">
-        <v>6928039</v>
+        <v>6928051</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2455,12 +2455,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132471858</v>
+        <v>128386879</v>
       </c>
       <c r="B19" t="n">
-        <v>92245</v>
+        <v>92208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,13 +2532,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589187</v>
+        <v>588983</v>
       </c>
       <c r="R19" t="n">
-        <v>6928156</v>
+        <v>6928039</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2552,22 +2562,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,7 +2594,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132785107</v>
+        <v>132471858</v>
       </c>
       <c r="B20" t="n">
         <v>92245</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589264</v>
+        <v>589187</v>
       </c>
       <c r="R20" t="n">
-        <v>6928250</v>
+        <v>6928156</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2659,22 +2659,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2701,32 +2701,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132471859</v>
+        <v>132785107</v>
       </c>
       <c r="B21" t="n">
-        <v>92689</v>
+        <v>92245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589194</v>
+        <v>589264</v>
       </c>
       <c r="R21" t="n">
-        <v>6928151</v>
+        <v>6928250</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -2808,10 +2808,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134822366</v>
+        <v>132471859</v>
       </c>
       <c r="B22" t="n">
-        <v>97526</v>
+        <v>92689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,41 +2819,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>990</v>
+        <v>898</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589191</v>
+        <v>589194</v>
       </c>
       <c r="R22" t="n">
-        <v>6928154</v>
+        <v>6928151</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2877,17 +2873,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Satt på samma granlåga som rosenticka och blackticka</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2896,7 +2897,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134822383</v>
+        <v>134822366</v>
       </c>
       <c r="B23" t="n">
         <v>97526</v>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589190</v>
+        <v>589191</v>
       </c>
       <c r="R23" t="n">
-        <v>6928155</v>
+        <v>6928154</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,6 +2990,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Satt på samma granlåga som rosenticka och blackticka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,7 +3022,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135039352</v>
+        <v>134822383</v>
       </c>
       <c r="B24" t="n">
         <v>97526</v>
@@ -3052,17 +3057,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589274</v>
+        <v>589190</v>
       </c>
       <c r="R24" t="n">
-        <v>6928255</v>
+        <v>6928155</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3086,29 +3091,19 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>08:31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>08:31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
@@ -3129,48 +3124,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126612297</v>
+        <v>135039352</v>
       </c>
       <c r="B25" t="n">
-        <v>91909</v>
+        <v>97526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>990</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589007</v>
+        <v>589274</v>
       </c>
       <c r="R25" t="n">
-        <v>6928045</v>
+        <v>6928255</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3194,12 +3193,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3208,6 +3217,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3226,7 +3236,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128386936</v>
+        <v>126612297</v>
       </c>
       <c r="B26" t="n">
         <v>91909</v>
@@ -3261,7 +3271,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588976</v>
+        <v>589007</v>
       </c>
       <c r="R26" t="n">
         <v>6928045</v>
@@ -3291,12 +3301,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3323,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132471854</v>
+        <v>128386936</v>
       </c>
       <c r="B27" t="n">
-        <v>91974</v>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3358,13 +3368,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589097</v>
+        <v>588976</v>
       </c>
       <c r="R27" t="n">
-        <v>6928084</v>
+        <v>6928045</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3388,22 +3398,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,7 +3430,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132785102</v>
+        <v>132471854</v>
       </c>
       <c r="B28" t="n">
         <v>91974</v>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589261</v>
+        <v>589097</v>
       </c>
       <c r="R28" t="n">
-        <v>6928183</v>
+        <v>6928084</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3495,22 +3495,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3537,7 +3537,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132785105</v>
+        <v>132785102</v>
       </c>
       <c r="B29" t="n">
         <v>91974</v>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589267</v>
+        <v>589261</v>
       </c>
       <c r="R29" t="n">
-        <v>6928248</v>
+        <v>6928183</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3644,32 +3644,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134822272</v>
+        <v>132785105</v>
       </c>
       <c r="B30" t="n">
-        <v>91988</v>
+        <v>91974</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589103</v>
+        <v>589267</v>
       </c>
       <c r="R30" t="n">
-        <v>6928097</v>
+        <v>6928248</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3709,22 +3709,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,32 +3751,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128386897</v>
+        <v>134822272</v>
       </c>
       <c r="B31" t="n">
-        <v>92369</v>
+        <v>91988</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3786,13 +3786,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588976</v>
+        <v>589103</v>
       </c>
       <c r="R31" t="n">
-        <v>6928045</v>
+        <v>6928097</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3816,12 +3816,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3848,32 +3858,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132471857</v>
+        <v>135276302</v>
       </c>
       <c r="B32" t="n">
-        <v>92406</v>
+        <v>91988</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3883,13 +3893,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589184</v>
+        <v>589236</v>
       </c>
       <c r="R32" t="n">
-        <v>6928132</v>
+        <v>6928161</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3913,22 +3923,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3955,10 +3965,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132785106</v>
+        <v>128386897</v>
       </c>
       <c r="B33" t="n">
-        <v>92406</v>
+        <v>92369</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,13 +4000,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589265</v>
+        <v>588976</v>
       </c>
       <c r="R33" t="n">
-        <v>6928249</v>
+        <v>6928045</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4020,22 +4030,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,10 +4062,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132471841</v>
+        <v>132471857</v>
       </c>
       <c r="B34" t="n">
-        <v>83222</v>
+        <v>92406</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4073,21 +4073,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4097,13 +4097,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589035</v>
+        <v>589184</v>
       </c>
       <c r="R34" t="n">
-        <v>6928084</v>
+        <v>6928132</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4127,22 +4127,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4169,10 +4169,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132471849</v>
+        <v>132785106</v>
       </c>
       <c r="B35" t="n">
-        <v>83222</v>
+        <v>92406</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4180,21 +4180,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4204,13 +4204,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>588991</v>
+        <v>589265</v>
       </c>
       <c r="R35" t="n">
-        <v>6928075</v>
+        <v>6928249</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4234,22 +4234,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4276,7 +4276,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132471851</v>
+        <v>132471841</v>
       </c>
       <c r="B36" t="n">
         <v>83222</v>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>588994</v>
+        <v>589035</v>
       </c>
       <c r="R36" t="n">
-        <v>6928051</v>
+        <v>6928084</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4383,7 +4383,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132471852</v>
+        <v>132471849</v>
       </c>
       <c r="B37" t="n">
         <v>83222</v>
@@ -4418,13 +4418,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>588989</v>
+        <v>588991</v>
       </c>
       <c r="R37" t="n">
-        <v>6928023</v>
+        <v>6928075</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4448,22 +4448,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4490,7 +4490,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132471856</v>
+        <v>132471851</v>
       </c>
       <c r="B38" t="n">
         <v>83222</v>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589129</v>
+        <v>588994</v>
       </c>
       <c r="R38" t="n">
-        <v>6928104</v>
+        <v>6928051</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4555,22 +4555,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4597,7 +4597,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132471861</v>
+        <v>132471852</v>
       </c>
       <c r="B39" t="n">
         <v>83222</v>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589209</v>
+        <v>588989</v>
       </c>
       <c r="R39" t="n">
-        <v>6928161</v>
+        <v>6928023</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4704,7 +4704,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132785097</v>
+        <v>132471856</v>
       </c>
       <c r="B40" t="n">
         <v>83222</v>
@@ -4739,13 +4739,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589067</v>
+        <v>589129</v>
       </c>
       <c r="R40" t="n">
-        <v>6928056</v>
+        <v>6928104</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4769,22 +4769,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4811,7 +4811,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132785098</v>
+        <v>132471861</v>
       </c>
       <c r="B41" t="n">
         <v>83222</v>
@@ -4846,13 +4846,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589103</v>
+        <v>589209</v>
       </c>
       <c r="R41" t="n">
-        <v>6928082</v>
+        <v>6928161</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4876,22 +4876,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4918,7 +4918,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133862333</v>
+        <v>132785097</v>
       </c>
       <c r="B42" t="n">
         <v>83222</v>
@@ -4953,13 +4953,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589103</v>
+        <v>589067</v>
       </c>
       <c r="R42" t="n">
-        <v>6928108</v>
+        <v>6928056</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4983,22 +4983,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5025,7 +5025,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134822274</v>
+        <v>132785098</v>
       </c>
       <c r="B43" t="n">
         <v>83222</v>
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589003</v>
+        <v>589103</v>
       </c>
       <c r="R43" t="n">
-        <v>6928057</v>
+        <v>6928082</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5090,22 +5090,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5132,7 +5132,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135039348</v>
+        <v>133862333</v>
       </c>
       <c r="B44" t="n">
         <v>83222</v>
@@ -5167,13 +5167,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589143</v>
+        <v>589103</v>
       </c>
       <c r="R44" t="n">
-        <v>6928120</v>
+        <v>6928108</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5197,22 +5197,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5239,32 +5239,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126611830</v>
+        <v>134822274</v>
       </c>
       <c r="B45" t="n">
-        <v>97231</v>
+        <v>83222</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5274,13 +5274,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>588956</v>
+        <v>589003</v>
       </c>
       <c r="R45" t="n">
-        <v>6927950</v>
+        <v>6928057</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5304,12 +5304,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5336,32 +5346,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126612079</v>
+        <v>135039348</v>
       </c>
       <c r="B46" t="n">
-        <v>97231</v>
+        <v>83222</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5371,13 +5381,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>588992</v>
+        <v>589143</v>
       </c>
       <c r="R46" t="n">
-        <v>6928003</v>
+        <v>6928120</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5401,12 +5411,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5433,7 +5453,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126613094</v>
+        <v>126611830</v>
       </c>
       <c r="B47" t="n">
         <v>97231</v>
@@ -5468,10 +5488,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589196</v>
+        <v>588956</v>
       </c>
       <c r="R47" t="n">
-        <v>6928142</v>
+        <v>6927950</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5530,7 +5550,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128387088</v>
+        <v>126612079</v>
       </c>
       <c r="B48" t="n">
         <v>97231</v>
@@ -5565,10 +5585,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>588996</v>
+        <v>588992</v>
       </c>
       <c r="R48" t="n">
-        <v>6928070</v>
+        <v>6928003</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5595,12 +5615,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5627,10 +5647,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128385756</v>
+        <v>126613094</v>
       </c>
       <c r="B49" t="n">
-        <v>91680</v>
+        <v>97231</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5638,21 +5658,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3215</v>
+        <v>2869</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5662,10 +5682,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>588904</v>
+        <v>589196</v>
       </c>
       <c r="R49" t="n">
-        <v>6927932</v>
+        <v>6928142</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5692,12 +5712,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5724,32 +5744,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126614196</v>
+        <v>128387088</v>
       </c>
       <c r="B50" t="n">
-        <v>93197</v>
+        <v>97231</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5759,10 +5779,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>588872</v>
+        <v>588996</v>
       </c>
       <c r="R50" t="n">
-        <v>6927920</v>
+        <v>6928070</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5789,12 +5809,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5821,48 +5841,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133549777</v>
+        <v>128385756</v>
       </c>
       <c r="B51" t="n">
-        <v>93271</v>
+        <v>91680</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lakatjärnsböcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>588965</v>
+        <v>588904</v>
       </c>
       <c r="R51" t="n">
-        <v>6928016</v>
+        <v>6927932</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5886,22 +5906,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5928,32 +5938,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132785099</v>
+        <v>126614196</v>
       </c>
       <c r="B52" t="n">
-        <v>91937</v>
+        <v>93197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5963,13 +5973,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589133</v>
+        <v>588872</v>
       </c>
       <c r="R52" t="n">
-        <v>6928102</v>
+        <v>6927920</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5993,22 +6003,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6035,48 +6035,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126611375</v>
+        <v>133549777</v>
       </c>
       <c r="B53" t="n">
-        <v>79327</v>
+        <v>93271</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsböcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>588891</v>
+        <v>588965</v>
       </c>
       <c r="R53" t="n">
-        <v>6927920</v>
+        <v>6928016</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6100,12 +6100,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6132,32 +6142,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126612201</v>
+        <v>132785099</v>
       </c>
       <c r="B54" t="n">
-        <v>79327</v>
+        <v>91937</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6167,13 +6177,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>588980</v>
+        <v>589133</v>
       </c>
       <c r="R54" t="n">
-        <v>6928023</v>
+        <v>6928102</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6197,12 +6207,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6229,10 +6249,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132471837</v>
+        <v>126611375</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6264,13 +6284,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>588926</v>
+        <v>588891</v>
       </c>
       <c r="R55" t="n">
-        <v>6927968</v>
+        <v>6927920</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6294,22 +6314,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6336,10 +6346,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132471838</v>
+        <v>126612201</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6371,13 +6381,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>588968</v>
+        <v>588980</v>
       </c>
       <c r="R56" t="n">
-        <v>6928015</v>
+        <v>6928023</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6401,22 +6411,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>18:17</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>18:17</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6443,7 +6443,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132471839</v>
+        <v>132471837</v>
       </c>
       <c r="B57" t="n">
         <v>79373</v>
@@ -6478,13 +6478,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589000</v>
+        <v>588926</v>
       </c>
       <c r="R57" t="n">
-        <v>6928044</v>
+        <v>6927968</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6550,7 +6550,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132471840</v>
+        <v>132471838</v>
       </c>
       <c r="B58" t="n">
         <v>79373</v>
@@ -6585,13 +6585,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589025</v>
+        <v>588968</v>
       </c>
       <c r="R58" t="n">
-        <v>6928084</v>
+        <v>6928015</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6657,7 +6657,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132471843</v>
+        <v>132471839</v>
       </c>
       <c r="B59" t="n">
         <v>79373</v>
@@ -6692,13 +6692,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589031</v>
+        <v>589000</v>
       </c>
       <c r="R59" t="n">
-        <v>6928096</v>
+        <v>6928044</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6764,7 +6764,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132471845</v>
+        <v>132471840</v>
       </c>
       <c r="B60" t="n">
         <v>79373</v>
@@ -6799,13 +6799,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589053</v>
+        <v>589025</v>
       </c>
       <c r="R60" t="n">
-        <v>6928105</v>
+        <v>6928084</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6871,7 +6871,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132471853</v>
+        <v>132471843</v>
       </c>
       <c r="B61" t="n">
         <v>79373</v>
@@ -6906,13 +6906,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>589101</v>
+        <v>589031</v>
       </c>
       <c r="R61" t="n">
-        <v>6928090</v>
+        <v>6928096</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6936,22 +6936,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6978,7 +6978,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132785101</v>
+        <v>132471845</v>
       </c>
       <c r="B62" t="n">
         <v>79373</v>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589255</v>
+        <v>589053</v>
       </c>
       <c r="R62" t="n">
-        <v>6928176</v>
+        <v>6928105</v>
       </c>
       <c r="S62" t="n">
         <v>6</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7085,7 +7085,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135039349</v>
+        <v>132471853</v>
       </c>
       <c r="B63" t="n">
         <v>79373</v>
@@ -7120,13 +7120,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589245</v>
+        <v>589101</v>
       </c>
       <c r="R63" t="n">
-        <v>6928180</v>
+        <v>6928090</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7150,22 +7150,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7192,32 +7192,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132785117</v>
+        <v>132785101</v>
       </c>
       <c r="B64" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7227,13 +7227,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>588910</v>
+        <v>589255</v>
       </c>
       <c r="R64" t="n">
-        <v>6927968</v>
+        <v>6928176</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7257,22 +7257,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7299,32 +7299,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133862337</v>
+        <v>135039349</v>
       </c>
       <c r="B65" t="n">
-        <v>83341</v>
+        <v>79373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7334,13 +7334,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>589181</v>
+        <v>589245</v>
       </c>
       <c r="R65" t="n">
-        <v>6928156</v>
+        <v>6928180</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7364,22 +7364,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7406,48 +7406,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133549784</v>
+        <v>135276295</v>
       </c>
       <c r="B66" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lakatjärnsböcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589052</v>
+        <v>588922</v>
       </c>
       <c r="R66" t="n">
-        <v>6928089</v>
+        <v>6927932</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7471,22 +7471,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7513,45 +7513,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133549786</v>
+        <v>132785117</v>
       </c>
       <c r="B67" t="n">
-        <v>83358</v>
+        <v>79397</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lakatjärnsböcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589041</v>
+        <v>588910</v>
       </c>
       <c r="R67" t="n">
-        <v>6928112</v>
+        <v>6927968</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7578,22 +7578,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7620,32 +7620,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133862328</v>
+        <v>133862337</v>
       </c>
       <c r="B68" t="n">
-        <v>83358</v>
+        <v>83341</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7655,13 +7655,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>589014</v>
+        <v>589181</v>
       </c>
       <c r="R68" t="n">
-        <v>6928075</v>
+        <v>6928156</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7727,7 +7727,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133862332</v>
+        <v>133549784</v>
       </c>
       <c r="B69" t="n">
         <v>83358</v>
@@ -7758,17 +7758,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsböcken, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>589043</v>
+        <v>589052</v>
       </c>
       <c r="R69" t="n">
-        <v>6928128</v>
+        <v>6928089</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7792,22 +7792,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7834,7 +7834,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133862334</v>
+        <v>133549786</v>
       </c>
       <c r="B70" t="n">
         <v>83358</v>
@@ -7865,14 +7865,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsböcken, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589124</v>
+        <v>589041</v>
       </c>
       <c r="R70" t="n">
-        <v>6928125</v>
+        <v>6928112</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7899,22 +7899,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7941,7 +7941,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133862335</v>
+        <v>133862328</v>
       </c>
       <c r="B71" t="n">
         <v>83358</v>
@@ -7976,13 +7976,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589132</v>
+        <v>589014</v>
       </c>
       <c r="R71" t="n">
-        <v>6928128</v>
+        <v>6928075</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8048,7 +8048,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133862338</v>
+        <v>133862332</v>
       </c>
       <c r="B72" t="n">
         <v>83358</v>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>589113</v>
+        <v>589043</v>
       </c>
       <c r="R72" t="n">
-        <v>6928125</v>
+        <v>6928128</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8155,7 +8155,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134822270</v>
+        <v>133862334</v>
       </c>
       <c r="B73" t="n">
         <v>83358</v>
@@ -8190,10 +8190,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589020</v>
+        <v>589124</v>
       </c>
       <c r="R73" t="n">
-        <v>6928074</v>
+        <v>6928125</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8220,22 +8220,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8262,7 +8262,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135039347</v>
+        <v>133862335</v>
       </c>
       <c r="B74" t="n">
         <v>83358</v>
@@ -8297,13 +8297,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589029</v>
+        <v>589132</v>
       </c>
       <c r="R74" t="n">
-        <v>6928060</v>
+        <v>6928128</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8327,22 +8327,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8369,10 +8369,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132785115</v>
+        <v>133862338</v>
       </c>
       <c r="B75" t="n">
-        <v>79130</v>
+        <v>83358</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8380,21 +8380,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8404,13 +8404,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>589083</v>
+        <v>589113</v>
       </c>
       <c r="R75" t="n">
-        <v>6928098</v>
+        <v>6928125</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8434,22 +8434,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8476,32 +8476,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132785104</v>
+        <v>134822270</v>
       </c>
       <c r="B76" t="n">
-        <v>80382</v>
+        <v>83358</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8511,10 +8511,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>589285</v>
+        <v>589020</v>
       </c>
       <c r="R76" t="n">
-        <v>6928228</v>
+        <v>6928074</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8541,22 +8541,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8583,10 +8583,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126612522</v>
+        <v>135039347</v>
       </c>
       <c r="B77" t="n">
-        <v>80432</v>
+        <v>83358</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8594,21 +8594,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8618,13 +8618,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>589049</v>
+        <v>589029</v>
       </c>
       <c r="R77" t="n">
-        <v>6928131</v>
+        <v>6928060</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8648,12 +8648,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8680,10 +8690,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128387885</v>
+        <v>132785115</v>
       </c>
       <c r="B78" t="n">
-        <v>80432</v>
+        <v>79130</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8691,42 +8701,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589049</v>
+        <v>589083</v>
       </c>
       <c r="R78" t="n">
-        <v>6928118</v>
+        <v>6928098</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8750,12 +8755,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8782,32 +8797,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132471848</v>
+        <v>132785104</v>
       </c>
       <c r="B79" t="n">
-        <v>80488</v>
+        <v>80382</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8817,13 +8832,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589060</v>
+        <v>589285</v>
       </c>
       <c r="R79" t="n">
-        <v>6928116</v>
+        <v>6928228</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8847,22 +8862,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8889,10 +8904,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132471862</v>
+        <v>126612522</v>
       </c>
       <c r="B80" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8924,13 +8939,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589162</v>
+        <v>589049</v>
       </c>
       <c r="R80" t="n">
-        <v>6928150</v>
+        <v>6928131</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8954,22 +8969,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8996,10 +9001,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132785108</v>
+        <v>128387885</v>
       </c>
       <c r="B81" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9025,19 +9030,24 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>589231</v>
+        <v>589049</v>
       </c>
       <c r="R81" t="n">
-        <v>6928252</v>
+        <v>6928118</v>
       </c>
       <c r="S81" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9061,27 +9071,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9108,7 +9103,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132785110</v>
+        <v>132471848</v>
       </c>
       <c r="B82" t="n">
         <v>80488</v>
@@ -9143,13 +9138,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>589217</v>
+        <v>589060</v>
       </c>
       <c r="R82" t="n">
-        <v>6928191</v>
+        <v>6928116</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9173,22 +9168,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9215,7 +9210,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132785113</v>
+        <v>132471862</v>
       </c>
       <c r="B83" t="n">
         <v>80488</v>
@@ -9250,10 +9245,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>589219</v>
+        <v>589162</v>
       </c>
       <c r="R83" t="n">
-        <v>6928180</v>
+        <v>6928150</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9280,7 +9275,7 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
@@ -9290,7 +9285,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
@@ -9322,7 +9317,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134822269</v>
+        <v>132785108</v>
       </c>
       <c r="B84" t="n">
         <v>80488</v>
@@ -9357,13 +9352,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589103</v>
+        <v>589231</v>
       </c>
       <c r="R84" t="n">
-        <v>6928090</v>
+        <v>6928252</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9387,22 +9382,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9429,7 +9429,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134822273</v>
+        <v>132785110</v>
       </c>
       <c r="B85" t="n">
         <v>80488</v>
@@ -9464,10 +9464,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589113</v>
+        <v>589217</v>
       </c>
       <c r="R85" t="n">
-        <v>6928086</v>
+        <v>6928191</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9494,22 +9494,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9536,32 +9536,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134822271</v>
+        <v>132785113</v>
       </c>
       <c r="B86" t="n">
-        <v>79629</v>
+        <v>80488</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9571,10 +9571,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589065</v>
+        <v>589219</v>
       </c>
       <c r="R86" t="n">
-        <v>6928080</v>
+        <v>6928180</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9601,22 +9601,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9625,7 +9625,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9644,32 +9643,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135039346</v>
+        <v>134822269</v>
       </c>
       <c r="B87" t="n">
-        <v>79629</v>
+        <v>80488</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9679,10 +9678,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>589029</v>
+        <v>589103</v>
       </c>
       <c r="R87" t="n">
-        <v>6928060</v>
+        <v>6928090</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9709,22 +9708,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9751,32 +9750,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133862331</v>
+        <v>134822273</v>
       </c>
       <c r="B88" t="n">
-        <v>80492</v>
+        <v>80488</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9786,10 +9785,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>589025</v>
+        <v>589113</v>
       </c>
       <c r="R88" t="n">
-        <v>6928117</v>
+        <v>6928086</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9816,22 +9815,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9858,10 +9857,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128387896</v>
+        <v>134822271</v>
       </c>
       <c r="B89" t="n">
-        <v>80461</v>
+        <v>79629</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9869,21 +9868,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9893,13 +9892,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589035</v>
+        <v>589065</v>
       </c>
       <c r="R89" t="n">
-        <v>6928128</v>
+        <v>6928080</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9923,12 +9922,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9937,6 +9946,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9955,10 +9965,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132471847</v>
+        <v>135039346</v>
       </c>
       <c r="B90" t="n">
-        <v>80493</v>
+        <v>79629</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9966,21 +9976,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9990,10 +10000,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589055</v>
+        <v>589029</v>
       </c>
       <c r="R90" t="n">
-        <v>6928107</v>
+        <v>6928060</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10020,22 +10030,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10062,10 +10072,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132785109</v>
+        <v>133862331</v>
       </c>
       <c r="B91" t="n">
-        <v>80493</v>
+        <v>80492</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10073,21 +10083,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10097,10 +10107,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>589218</v>
+        <v>589025</v>
       </c>
       <c r="R91" t="n">
-        <v>6928197</v>
+        <v>6928117</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10127,22 +10137,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10169,10 +10179,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132785111</v>
+        <v>128387896</v>
       </c>
       <c r="B92" t="n">
-        <v>80493</v>
+        <v>80461</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10204,13 +10214,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>589217</v>
+        <v>589035</v>
       </c>
       <c r="R92" t="n">
-        <v>6928189</v>
+        <v>6928128</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10234,22 +10244,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10276,10 +10276,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132785112</v>
+        <v>132471847</v>
       </c>
       <c r="B93" t="n">
-        <v>80499</v>
+        <v>80493</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10287,21 +10287,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>589220</v>
+        <v>589055</v>
       </c>
       <c r="R93" t="n">
-        <v>6928181</v>
+        <v>6928107</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10341,22 +10341,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10383,10 +10383,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132471864</v>
+        <v>132785109</v>
       </c>
       <c r="B94" t="n">
-        <v>80500</v>
+        <v>80493</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10394,21 +10394,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10418,10 +10418,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>589164</v>
+        <v>589218</v>
       </c>
       <c r="R94" t="n">
-        <v>6928149</v>
+        <v>6928197</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10448,22 +10448,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10490,56 +10490,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126611902</v>
+        <v>132785111</v>
       </c>
       <c r="B95" t="n">
-        <v>57874</v>
+        <v>80493</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100001</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>588956</v>
+        <v>589217</v>
       </c>
       <c r="R95" t="n">
-        <v>6927950</v>
+        <v>6928189</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10563,12 +10555,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10595,53 +10597,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126611439</v>
+        <v>132785112</v>
       </c>
       <c r="B96" t="n">
-        <v>57953</v>
+        <v>80499</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>588906</v>
+        <v>589220</v>
       </c>
       <c r="R96" t="n">
-        <v>6927920</v>
+        <v>6928181</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10665,17 +10662,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10702,53 +10704,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126612501</v>
+        <v>132471864</v>
       </c>
       <c r="B97" t="n">
-        <v>57953</v>
+        <v>80500</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>589049</v>
+        <v>589164</v>
       </c>
       <c r="R97" t="n">
-        <v>6928118</v>
+        <v>6928149</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10772,17 +10769,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10809,10 +10811,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126612557</v>
+        <v>126611902</v>
       </c>
       <c r="B98" t="n">
-        <v>57953</v>
+        <v>57874</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10820,16 +10822,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10838,21 +10840,24 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>589061</v>
+        <v>588956</v>
       </c>
       <c r="R98" t="n">
-        <v>6928145</v>
+        <v>6927950</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10885,11 +10890,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10916,10 +10916,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126612632</v>
+        <v>135276296</v>
       </c>
       <c r="B99" t="n">
-        <v>57953</v>
+        <v>57896</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10927,16 +10927,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10944,25 +10944,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>589097</v>
+        <v>588973</v>
       </c>
       <c r="R99" t="n">
-        <v>6928100</v>
+        <v>6928144</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10986,17 +10993,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11023,7 +11035,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126612730</v>
+        <v>126611439</v>
       </c>
       <c r="B100" t="n">
         <v>57953</v>
@@ -11063,10 +11075,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>589123</v>
+        <v>588906</v>
       </c>
       <c r="R100" t="n">
-        <v>6928089</v>
+        <v>6927920</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11103,7 +11115,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Årsfärska</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11130,7 +11142,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126612770</v>
+        <v>126612501</v>
       </c>
       <c r="B101" t="n">
         <v>57953</v>
@@ -11161,7 +11173,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11170,10 +11182,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>589131</v>
+        <v>589049</v>
       </c>
       <c r="R101" t="n">
-        <v>6928090</v>
+        <v>6928118</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11237,7 +11249,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126613234</v>
+        <v>126612557</v>
       </c>
       <c r="B102" t="n">
         <v>57953</v>
@@ -11268,7 +11280,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11277,10 +11289,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>589242</v>
+        <v>589061</v>
       </c>
       <c r="R102" t="n">
-        <v>6928172</v>
+        <v>6928145</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11344,7 +11356,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126613396</v>
+        <v>126612632</v>
       </c>
       <c r="B103" t="n">
         <v>57953</v>
@@ -11384,10 +11396,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>589261</v>
+        <v>589097</v>
       </c>
       <c r="R103" t="n">
-        <v>6928272</v>
+        <v>6928100</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11451,7 +11463,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126613429</v>
+        <v>126612730</v>
       </c>
       <c r="B104" t="n">
         <v>57953</v>
@@ -11482,7 +11494,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11491,10 +11503,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>589240</v>
+        <v>589123</v>
       </c>
       <c r="R104" t="n">
-        <v>6928277</v>
+        <v>6928089</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11531,7 +11543,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.  Årsfärska</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11558,7 +11570,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126613466</v>
+        <v>126612770</v>
       </c>
       <c r="B105" t="n">
         <v>57953</v>
@@ -11598,10 +11610,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>589242</v>
+        <v>589131</v>
       </c>
       <c r="R105" t="n">
-        <v>6928272</v>
+        <v>6928090</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11665,7 +11677,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126613641</v>
+        <v>126613234</v>
       </c>
       <c r="B106" t="n">
         <v>57953</v>
@@ -11705,10 +11717,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>589253</v>
+        <v>589242</v>
       </c>
       <c r="R106" t="n">
-        <v>6928222</v>
+        <v>6928172</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11772,7 +11784,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126648165</v>
+        <v>126613396</v>
       </c>
       <c r="B107" t="n">
         <v>57953</v>
@@ -11801,24 +11813,21 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>589257</v>
+        <v>589261</v>
       </c>
       <c r="R107" t="n">
-        <v>6928233</v>
+        <v>6928272</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11855,7 +11864,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Fjädrar från tretåig hackspett</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11882,7 +11891,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128386326</v>
+        <v>126613429</v>
       </c>
       <c r="B108" t="n">
         <v>57953</v>
@@ -11913,7 +11922,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -11922,10 +11931,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>588973</v>
+        <v>589240</v>
       </c>
       <c r="R108" t="n">
-        <v>6928008</v>
+        <v>6928277</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11952,12 +11961,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -11989,7 +11998,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128386843</v>
+        <v>126613466</v>
       </c>
       <c r="B109" t="n">
         <v>57953</v>
@@ -12029,10 +12038,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>588976</v>
+        <v>589242</v>
       </c>
       <c r="R109" t="n">
-        <v>6928045</v>
+        <v>6928272</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12059,12 +12068,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -12096,7 +12105,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128386976</v>
+        <v>126613641</v>
       </c>
       <c r="B110" t="n">
         <v>57953</v>
@@ -12136,10 +12145,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>589007</v>
+        <v>589253</v>
       </c>
       <c r="R110" t="n">
-        <v>6928045</v>
+        <v>6928222</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12166,12 +12175,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -12203,7 +12212,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128387786</v>
+        <v>126648165</v>
       </c>
       <c r="B111" t="n">
         <v>57953</v>
@@ -12232,21 +12241,24 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>589011</v>
+        <v>589257</v>
       </c>
       <c r="R111" t="n">
-        <v>6928137</v>
+        <v>6928233</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12273,17 +12285,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Fjädrar från tretåig hackspett</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12310,7 +12322,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128388697</v>
+        <v>128386326</v>
       </c>
       <c r="B112" t="n">
         <v>57953</v>
@@ -12338,14 +12350,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -12354,10 +12362,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>589084</v>
+        <v>588973</v>
       </c>
       <c r="R112" t="n">
-        <v>6928101</v>
+        <v>6928008</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12390,6 +12398,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12416,7 +12429,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128390318</v>
+        <v>128386843</v>
       </c>
       <c r="B113" t="n">
         <v>57953</v>
@@ -12447,7 +12460,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -12456,10 +12469,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>589269</v>
+        <v>588976</v>
       </c>
       <c r="R113" t="n">
-        <v>6928187</v>
+        <v>6928045</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12523,10 +12536,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132758633</v>
+        <v>128386976</v>
       </c>
       <c r="B114" t="n">
-        <v>57954</v>
+        <v>57953</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12551,32 +12564,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>589149</v>
+        <v>589007</v>
       </c>
       <c r="R114" t="n">
-        <v>6928126</v>
+        <v>6928045</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12600,17 +12606,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Två tretåiga hackspettar trummar till varandra.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12637,10 +12643,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132785114</v>
+        <v>128387786</v>
       </c>
       <c r="B115" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12666,27 +12672,24 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>589134</v>
+        <v>589011</v>
       </c>
       <c r="R115" t="n">
-        <v>6928133</v>
+        <v>6928137</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12710,27 +12713,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ett färskt ringhack. Ser ut att vara årsfärskt. Blänkande genomskinlig kåda syns.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12757,10 +12750,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>134822268</v>
+        <v>128388697</v>
       </c>
       <c r="B116" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12785,28 +12778,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>588945</v>
+        <v>589084</v>
       </c>
       <c r="R116" t="n">
-        <v>6927968</v>
+        <v>6928101</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12830,27 +12824,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12877,10 +12856,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>134822275</v>
+        <v>128390318</v>
       </c>
       <c r="B117" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12906,27 +12885,24 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>588946</v>
+        <v>589269</v>
       </c>
       <c r="R117" t="n">
-        <v>6927972</v>
+        <v>6928187</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12950,27 +12926,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12997,10 +12963,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135039353</v>
+        <v>132758633</v>
       </c>
       <c r="B118" t="n">
-        <v>57975</v>
+        <v>57954</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13025,28 +12991,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>589224</v>
+        <v>589149</v>
       </c>
       <c r="R118" t="n">
-        <v>6928208</v>
+        <v>6928126</v>
       </c>
       <c r="S118" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13070,27 +13040,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>08:38</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>08:38</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Två tretåiga hackspettar trummar till varandra.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13117,7 +13077,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135039354</v>
+        <v>132785114</v>
       </c>
       <c r="B119" t="n">
         <v>57975</v>
@@ -13160,13 +13120,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>589225</v>
+        <v>589134</v>
       </c>
       <c r="R119" t="n">
-        <v>6928206</v>
+        <v>6928133</v>
       </c>
       <c r="S119" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13190,27 +13150,27 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Färskt ringhack på tall</t>
+          <t>Ett färskt ringhack. Ser ut att vara årsfärskt. Blänkande genomskinlig kåda syns.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13237,27 +13197,27 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>132471846</v>
+        <v>134822268</v>
       </c>
       <c r="B120" t="n">
-        <v>57153</v>
+        <v>57975</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -13265,16 +13225,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -13284,10 +13240,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>589057</v>
+        <v>588945</v>
       </c>
       <c r="R120" t="n">
-        <v>6928109</v>
+        <v>6927968</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13314,22 +13270,27 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13356,27 +13317,27 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132472074</v>
+        <v>134822275</v>
       </c>
       <c r="B121" t="n">
-        <v>57153</v>
+        <v>57975</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -13384,32 +13345,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>589050</v>
+        <v>588946</v>
       </c>
       <c r="R121" t="n">
-        <v>6928091</v>
+        <v>6927972</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13433,12 +13390,27 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13465,27 +13437,27 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132758709</v>
+        <v>135039353</v>
       </c>
       <c r="B122" t="n">
-        <v>57153</v>
+        <v>57975</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -13493,32 +13465,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>589115</v>
+        <v>589224</v>
       </c>
       <c r="R122" t="n">
-        <v>6928103</v>
+        <v>6928208</v>
       </c>
       <c r="S122" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13542,12 +13510,27 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13574,10 +13557,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128386396</v>
+        <v>135039354</v>
       </c>
       <c r="B123" t="n">
-        <v>58114</v>
+        <v>57975</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13585,42 +13568,45 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>588973</v>
+        <v>589225</v>
       </c>
       <c r="R123" t="n">
-        <v>6928008</v>
+        <v>6928206</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13644,12 +13630,27 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13676,10 +13677,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132471855</v>
+        <v>135276293</v>
       </c>
       <c r="B124" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13687,33 +13688,29 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -13723,10 +13720,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>589103</v>
+        <v>588876</v>
       </c>
       <c r="R124" t="n">
-        <v>6928093</v>
+        <v>6927854</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13753,22 +13750,27 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Ringhacken är på gränsen till att räknas som äldre, men det finns fortfarande en del intorkad kåda kvar varför jag rapporterar in dom som färska.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13795,32 +13797,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132758689</v>
+        <v>132471846</v>
       </c>
       <c r="B125" t="n">
-        <v>58136</v>
+        <v>57153</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -13838,17 +13840,17 @@
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
+          <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>589145</v>
+        <v>589057</v>
       </c>
       <c r="R125" t="n">
-        <v>6928113</v>
+        <v>6928109</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13872,12 +13874,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13904,32 +13916,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132785103</v>
+        <v>132472074</v>
       </c>
       <c r="B126" t="n">
-        <v>58136</v>
+        <v>57153</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -13947,17 +13959,17 @@
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>589277</v>
+        <v>589050</v>
       </c>
       <c r="R126" t="n">
-        <v>6928192</v>
+        <v>6928091</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13981,22 +13993,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14023,10 +14025,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126611997</v>
+        <v>132758709</v>
       </c>
       <c r="B127" t="n">
-        <v>99035</v>
+        <v>57153</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14034,41 +14036,49 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>588957</v>
+        <v>589115</v>
       </c>
       <c r="R127" t="n">
-        <v>6927988</v>
+        <v>6928103</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14092,12 +14102,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14124,37 +14134,38 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126612756</v>
+        <v>128386396</v>
       </c>
       <c r="B128" t="n">
-        <v>99035</v>
+        <v>58114</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14163,10 +14174,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>589123</v>
+        <v>588973</v>
       </c>
       <c r="R128" t="n">
-        <v>6928089</v>
+        <v>6928008</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14193,12 +14204,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14225,48 +14236,60 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126613513</v>
+        <v>132471855</v>
       </c>
       <c r="B129" t="n">
-        <v>106244</v>
+        <v>58136</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Lakatjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>589240</v>
+        <v>589103</v>
       </c>
       <c r="R129" t="n">
-        <v>6928277</v>
+        <v>6928093</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14290,12 +14313,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14322,48 +14355,60 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126612248</v>
+        <v>132758689</v>
       </c>
       <c r="B130" t="n">
-        <v>97983</v>
+        <v>58136</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lakatjärnsbäcken, Mpd</t>
+          <t>Lakatjärnsbäcken, Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>588993</v>
+        <v>589145</v>
       </c>
       <c r="R130" t="n">
-        <v>6928035</v>
+        <v>6928113</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14387,12 +14432,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14419,10 +14464,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128386182</v>
+        <v>132785103</v>
       </c>
       <c r="B131" t="n">
-        <v>93299</v>
+        <v>58136</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14430,26 +14475,35 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6332770</v>
+        <v>103021</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -14457,13 +14511,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>588927</v>
+        <v>589277</v>
       </c>
       <c r="R131" t="n">
-        <v>6927974</v>
+        <v>6928192</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14487,12 +14541,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14501,7 +14565,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14517,6 +14580,727 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>126611997</v>
+      </c>
+      <c r="B132" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>588957</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6927988</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>126612756</v>
+      </c>
+      <c r="B133" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>589123</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6928089</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>135276298</v>
+      </c>
+      <c r="B134" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>589245</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6928259</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>13 ex. 2 blommar</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>135276300</v>
+      </c>
+      <c r="B135" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>589238</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6928278</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>6 ex</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>126613513</v>
+      </c>
+      <c r="B136" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>589240</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6928277</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>126612248</v>
+      </c>
+      <c r="B137" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>588993</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6928035</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128386182</v>
+      </c>
+      <c r="B138" t="n">
+        <v>93299</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Lakatjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>588927</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6927974</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY138"/>
+  <dimension ref="A1:AZ138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039350</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039351</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039355</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471945</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039345</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135276297</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471836</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1531,6 +1571,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471865</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1638,6 +1683,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785096</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,6 +1795,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785116</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1852,6 +1907,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133549781</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1959,6 +2019,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134822277</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2066,6 +2131,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133549785</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2173,6 +2243,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133862329</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2280,6 +2355,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133862330</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2387,6 +2467,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133862336</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2494,6 +2579,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133862327</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2591,6 +2681,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386879</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2698,6 +2793,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471858</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2805,6 +2905,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785107</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2912,6 +3017,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471859</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3019,6 +3129,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134822366</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3121,6 +3236,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134822383</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3233,6 +3353,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039352</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3330,6 +3455,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612297</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3427,6 +3557,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386936</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3534,6 +3669,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471854</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3641,6 +3781,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785102</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3748,6 +3893,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785105</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3855,6 +4005,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134822272</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3962,6 +4117,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135276302</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4059,6 +4219,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386897</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4166,6 +4331,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471857</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4273,6 +4443,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785106</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4380,6 +4555,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471841</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4487,6 +4667,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471849</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4594,6 +4779,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471851</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4701,6 +4891,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471852</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4808,6 +5003,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471856</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4915,6 +5115,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471861</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5022,6 +5227,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785097</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5129,6 +5339,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785098</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5236,6 +5451,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133862333</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5343,6 +5563,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134822274</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5450,6 +5675,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039348</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5547,6 +5777,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126611830</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5644,6 +5879,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612079</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5741,6 +5981,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126613094</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5838,6 +6083,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387088</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5935,6 +6185,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128385756</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6032,6 +6287,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126614196</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6139,6 +6399,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133549777</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6246,6 +6511,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785099</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6343,6 +6613,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126611375</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6440,6 +6715,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612201</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6547,6 +6827,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471837</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6654,6 +6939,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471838</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6761,6 +7051,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471839</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6868,6 +7163,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471840</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6975,6 +7275,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471843</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7082,6 +7387,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471845</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7189,6 +7499,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471853</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7296,6 +7611,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785101</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7403,6 +7723,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039349</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7510,6 +7835,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135276295</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7617,6 +7947,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785117</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7724,6 +8059,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133862337</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7831,6 +8171,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133549784</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7938,6 +8283,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133549786</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8045,6 +8395,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133862328</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8152,6 +8507,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133862332</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8259,6 +8619,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133862334</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8366,6 +8731,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133862335</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8473,6 +8843,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133862338</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8580,6 +8955,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134822270</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8687,6 +9067,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039347</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8794,6 +9179,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785115</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8901,6 +9291,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785104</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8998,6 +9393,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612522</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9100,6 +9500,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387885</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9207,6 +9612,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471848</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9314,6 +9724,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471862</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9426,6 +9841,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785108</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9533,6 +9953,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785110</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9640,6 +10065,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785113</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9747,6 +10177,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134822269</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9854,6 +10289,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134822273</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9962,6 +10402,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134822271</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10069,6 +10514,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039346</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10176,6 +10626,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133862331</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10273,6 +10728,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387896</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10380,6 +10840,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471847</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10487,6 +10952,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785109</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10594,6 +11064,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785111</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10701,6 +11176,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785112</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10808,6 +11288,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471864</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10913,6 +11398,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126611902</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11032,6 +11522,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135276296</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11139,6 +11634,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126611439</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11246,6 +11746,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612501</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11353,6 +11858,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612557</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11460,6 +11970,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612632</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11567,6 +12082,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612730</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11674,6 +12194,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612770</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11781,6 +12306,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126613234</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11888,6 +12418,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126613396</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11995,6 +12530,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126613429</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12102,6 +12642,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126613466</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12209,6 +12754,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126613641</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12319,6 +12869,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126648165</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12426,6 +12981,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386326</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12533,6 +13093,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386843</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12640,6 +13205,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386976</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12747,6 +13317,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128387786</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12853,6 +13428,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128388697</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12960,6 +13540,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128390318</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13074,6 +13659,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132758633</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13194,6 +13784,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785114</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13314,6 +13909,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134822268</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13434,6 +14034,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134822275</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13554,6 +14159,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039353</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13674,6 +14284,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039354</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13794,6 +14409,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135276293</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13913,6 +14533,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471846</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14022,6 +14647,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132472074</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14131,6 +14761,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132758709</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14233,6 +14868,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386396</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14352,6 +14992,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132471855</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14461,6 +15106,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132758689</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14580,6 +15230,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132785103</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14681,6 +15336,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126611997</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14782,6 +15442,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612756</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14894,6 +15559,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135276298</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15006,6 +15676,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135276300</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15103,6 +15778,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126613513</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15200,6 +15880,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126612248</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15301,8 +15986,152 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386182</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135039350</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135039351</v>
       </c>
       <c r="B3" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135039355</v>
       </c>
       <c r="B4" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135039345</v>
       </c>
       <c r="B6" t="n">
-        <v>92201</v>
+        <v>92243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>135276297</v>
       </c>
       <c r="B7" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135039352</v>
       </c>
       <c r="B25" t="n">
-        <v>97526</v>
+        <v>97570</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>135276302</v>
       </c>
       <c r="B32" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>135039348</v>
       </c>
       <c r="B46" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>135039349</v>
       </c>
       <c r="B65" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>135276295</v>
       </c>
       <c r="B66" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>135039347</v>
       </c>
       <c r="B77" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>135039346</v>
       </c>
       <c r="B90" t="n">
-        <v>79629</v>
+        <v>79667</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>135276296</v>
       </c>
       <c r="B99" t="n">
-        <v>57896</v>
+        <v>57901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>135039353</v>
       </c>
       <c r="B122" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>135039354</v>
       </c>
       <c r="B123" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>135276293</v>
       </c>
       <c r="B124" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>135276298</v>
       </c>
       <c r="B134" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>135276300</v>
       </c>
       <c r="B135" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135039350</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135039351</v>
       </c>
       <c r="B3" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135039355</v>
       </c>
       <c r="B4" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135039345</v>
       </c>
       <c r="B6" t="n">
-        <v>92243</v>
+        <v>92270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>135276297</v>
       </c>
       <c r="B7" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135039352</v>
       </c>
       <c r="B25" t="n">
-        <v>97570</v>
+        <v>97597</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>135276302</v>
       </c>
       <c r="B32" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>135039348</v>
       </c>
       <c r="B46" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>135039349</v>
       </c>
       <c r="B65" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>135276295</v>
       </c>
       <c r="B66" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>135039347</v>
       </c>
       <c r="B77" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>135039346</v>
       </c>
       <c r="B90" t="n">
-        <v>79667</v>
+        <v>79694</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>135276298</v>
       </c>
       <c r="B134" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>135276300</v>
       </c>
       <c r="B135" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 34866-2024 artfynd.xlsx
+++ b/artfynd/A 34866-2024 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>135276297</v>
       </c>
       <c r="B7" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135039352</v>
       </c>
       <c r="B25" t="n">
-        <v>97602</v>
+        <v>97604</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>135276302</v>
       </c>
       <c r="B32" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>135276298</v>
       </c>
       <c r="B134" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>135276300</v>
       </c>
       <c r="B135" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
